--- a/research/traditional_assets/database/data/france/france_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/france/france_oil_gas_distribution.xlsx
@@ -1409,7 +1409,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1546,22 +1546,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07484350764588704</v>
+        <v>0.07469014887677232</v>
       </c>
       <c r="C2">
-        <v>4944.800657047063</v>
+        <v>4913.725110992787</v>
       </c>
       <c r="D2">
-        <v>4620.100657047064</v>
+        <v>4638.511110992787</v>
       </c>
       <c r="E2">
-        <v>-16.1</v>
+        <v>33.386</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>49.486</v>
       </c>
       <c r="G2">
         <v>324.7</v>
@@ -1582,28 +1582,28 @@
         <v>330.89</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.4891458</v>
       </c>
       <c r="N2">
-        <v>330.89</v>
+        <v>328.4008542</v>
       </c>
       <c r="O2">
-        <v>82.72250000000001</v>
+        <v>82.10021355000001</v>
       </c>
       <c r="P2">
-        <v>248.1675</v>
+        <v>246.30064065</v>
       </c>
       <c r="Q2">
-        <v>255.3775</v>
+        <v>253.51064065</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07484350764588704</v>
+        <v>0.07506353421896195</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5704007501151668</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1620,7 +1620,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>132.9331532126403</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1628,22 +1628,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07469014887677232</v>
+        <v>0.07453679010765762</v>
       </c>
       <c r="C3">
-        <v>4913.725110992787</v>
+        <v>4882.796878121066</v>
       </c>
       <c r="D3">
-        <v>4638.511110992787</v>
+        <v>4657.068878121066</v>
       </c>
       <c r="E3">
-        <v>33.386</v>
+        <v>82.87200000000001</v>
       </c>
       <c r="F3">
-        <v>49.486</v>
+        <v>98.97200000000001</v>
       </c>
       <c r="G3">
         <v>324.7</v>
@@ -1664,28 +1664,28 @@
         <v>330.89</v>
       </c>
       <c r="M3">
-        <v>2.4891458</v>
+        <v>4.9782916</v>
       </c>
       <c r="N3">
-        <v>328.4008542</v>
+        <v>325.9117084000001</v>
       </c>
       <c r="O3">
-        <v>82.10021355000001</v>
+        <v>81.47792710000002</v>
       </c>
       <c r="P3">
-        <v>246.30064065</v>
+        <v>244.4337813</v>
       </c>
       <c r="Q3">
-        <v>253.51064065</v>
+        <v>251.6437813000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07506353421896195</v>
+        <v>0.07528805113026288</v>
       </c>
       <c r="T3">
-        <v>0.5704007501151668</v>
+        <v>0.574777002609529</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1702,7 +1702,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>132.9331532126403</v>
+        <v>66.46657660632013</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1710,22 +1710,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07453679010765762</v>
+        <v>0.07438343133854289</v>
       </c>
       <c r="C4">
-        <v>4882.796878121066</v>
+        <v>4852.017733647072</v>
       </c>
       <c r="D4">
-        <v>4657.068878121066</v>
+        <v>4675.775733647071</v>
       </c>
       <c r="E4">
-        <v>82.87200000000001</v>
+        <v>132.358</v>
       </c>
       <c r="F4">
-        <v>98.97200000000001</v>
+        <v>148.458</v>
       </c>
       <c r="G4">
         <v>324.7</v>
@@ -1746,28 +1746,28 @@
         <v>330.89</v>
       </c>
       <c r="M4">
-        <v>4.9782916</v>
+        <v>7.4674374</v>
       </c>
       <c r="N4">
-        <v>325.9117084000001</v>
+        <v>323.4225626</v>
       </c>
       <c r="O4">
-        <v>81.47792710000002</v>
+        <v>80.85564065000001</v>
       </c>
       <c r="P4">
-        <v>244.4337813</v>
+        <v>242.5669219500001</v>
       </c>
       <c r="Q4">
-        <v>251.6437813000001</v>
+        <v>249.7769219500001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07528805113026288</v>
+        <v>0.07551719725622978</v>
       </c>
       <c r="T4">
-        <v>0.574777002609529</v>
+        <v>0.5792434871140841</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>66.46657660632013</v>
+        <v>44.3110510708801</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1792,22 +1792,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07438343133854289</v>
+        <v>0.07423007256942817</v>
       </c>
       <c r="C5">
-        <v>4852.017733647072</v>
+        <v>4821.389481424245</v>
       </c>
       <c r="D5">
-        <v>4675.775733647071</v>
+        <v>4694.633481424245</v>
       </c>
       <c r="E5">
-        <v>132.358</v>
+        <v>181.844</v>
       </c>
       <c r="F5">
-        <v>148.458</v>
+        <v>197.944</v>
       </c>
       <c r="G5">
         <v>324.7</v>
@@ -1828,28 +1828,28 @@
         <v>330.89</v>
       </c>
       <c r="M5">
-        <v>7.4674374</v>
+        <v>9.956583200000001</v>
       </c>
       <c r="N5">
-        <v>323.4225626</v>
+        <v>320.9334168</v>
       </c>
       <c r="O5">
-        <v>80.85564065000001</v>
+        <v>80.23335420000001</v>
       </c>
       <c r="P5">
-        <v>242.5669219500001</v>
+        <v>240.7000626</v>
       </c>
       <c r="Q5">
-        <v>249.7769219500001</v>
+        <v>247.9100626</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07551719725622978</v>
+        <v>0.07575111725982102</v>
       </c>
       <c r="T5">
-        <v>0.5792434871140841</v>
+        <v>0.5838030233791509</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1866,7 +1866,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>44.3110510708801</v>
+        <v>33.23328830316007</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1874,22 +1874,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07423007256942817</v>
+        <v>0.07407671380031346</v>
       </c>
       <c r="C6">
-        <v>4821.389481424245</v>
+        <v>4790.913954524179</v>
       </c>
       <c r="D6">
-        <v>4694.633481424245</v>
+        <v>4713.643954524179</v>
       </c>
       <c r="E6">
-        <v>181.844</v>
+        <v>231.33</v>
       </c>
       <c r="F6">
-        <v>197.944</v>
+        <v>247.43</v>
       </c>
       <c r="G6">
         <v>324.7</v>
@@ -1910,28 +1910,28 @@
         <v>330.89</v>
       </c>
       <c r="M6">
-        <v>9.956583200000001</v>
+        <v>12.445729</v>
       </c>
       <c r="N6">
-        <v>320.9334168</v>
+        <v>318.444271</v>
       </c>
       <c r="O6">
-        <v>80.23335420000001</v>
+        <v>79.61106775</v>
       </c>
       <c r="P6">
-        <v>240.7000626</v>
+        <v>238.83320325</v>
       </c>
       <c r="Q6">
-        <v>247.9100626</v>
+        <v>246.04320325</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07575111725982102</v>
+        <v>0.07598996189506679</v>
       </c>
       <c r="T6">
-        <v>0.5838030233791509</v>
+        <v>0.588458549881377</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>33.23328830316007</v>
+        <v>26.58663064252805</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1956,22 +1956,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07407671380031346</v>
+        <v>0.07392335503119873</v>
       </c>
       <c r="C7">
-        <v>4790.913954524179</v>
+        <v>4760.593015830578</v>
       </c>
       <c r="D7">
-        <v>4713.643954524179</v>
+        <v>4732.809015830579</v>
       </c>
       <c r="E7">
-        <v>231.33</v>
+        <v>280.816</v>
       </c>
       <c r="F7">
-        <v>247.43</v>
+        <v>296.9160000000001</v>
       </c>
       <c r="G7">
         <v>324.7</v>
@@ -1992,28 +1992,28 @@
         <v>330.89</v>
       </c>
       <c r="M7">
-        <v>12.445729</v>
+        <v>14.9348748</v>
       </c>
       <c r="N7">
-        <v>318.444271</v>
+        <v>315.9551252000001</v>
       </c>
       <c r="O7">
-        <v>79.61106775</v>
+        <v>78.98878130000001</v>
       </c>
       <c r="P7">
-        <v>238.83320325</v>
+        <v>236.9663439</v>
       </c>
       <c r="Q7">
-        <v>246.04320325</v>
+        <v>244.1763439</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07598996189506679</v>
+        <v>0.07623388833106248</v>
       </c>
       <c r="T7">
-        <v>0.588458549881377</v>
+        <v>0.5932131301389696</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>26.58663064252805</v>
+        <v>22.15552553544005</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2038,22 +2038,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07392335503119873</v>
+        <v>0.07376999626208403</v>
       </c>
       <c r="C8">
-        <v>4760.593015830578</v>
+        <v>4730.428558647804</v>
       </c>
       <c r="D8">
-        <v>4732.809015830579</v>
+        <v>4752.130558647804</v>
       </c>
       <c r="E8">
-        <v>280.816</v>
+        <v>330.302</v>
       </c>
       <c r="F8">
-        <v>296.916</v>
+        <v>346.402</v>
       </c>
       <c r="G8">
         <v>324.7</v>
@@ -2074,28 +2074,28 @@
         <v>330.89</v>
       </c>
       <c r="M8">
-        <v>14.9348748</v>
+        <v>17.4240206</v>
       </c>
       <c r="N8">
-        <v>315.9551252000001</v>
+        <v>313.4659794</v>
       </c>
       <c r="O8">
-        <v>78.98878130000001</v>
+        <v>78.36649485000001</v>
       </c>
       <c r="P8">
-        <v>236.9663439</v>
+        <v>235.09948455</v>
       </c>
       <c r="Q8">
-        <v>244.1763439</v>
+        <v>242.30948455</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07623388833106248</v>
+        <v>0.07648306049686454</v>
       </c>
       <c r="T8">
-        <v>0.5932131301389696</v>
+        <v>0.5980699594343599</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>22.15552553544005</v>
+        <v>18.99045045894861</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2120,22 +2120,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07376999626208401</v>
+        <v>0.07361663749296932</v>
       </c>
       <c r="C9">
-        <v>4730.428558647805</v>
+        <v>4700.422507324374</v>
       </c>
       <c r="D9">
-        <v>4752.130558647806</v>
+        <v>4771.610507324374</v>
       </c>
       <c r="E9">
-        <v>330.302</v>
+        <v>379.788</v>
       </c>
       <c r="F9">
-        <v>346.402</v>
+        <v>395.888</v>
       </c>
       <c r="G9">
         <v>324.7</v>
@@ -2156,28 +2156,28 @@
         <v>330.89</v>
       </c>
       <c r="M9">
-        <v>17.4240206</v>
+        <v>19.9131664</v>
       </c>
       <c r="N9">
-        <v>313.4659794</v>
+        <v>310.9768336</v>
       </c>
       <c r="O9">
-        <v>78.36649485000001</v>
+        <v>77.74420840000001</v>
       </c>
       <c r="P9">
-        <v>235.09948455</v>
+        <v>233.2326252</v>
       </c>
       <c r="Q9">
-        <v>242.30948455</v>
+        <v>240.4426252</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07648306049686454</v>
+        <v>0.07673764944887969</v>
       </c>
       <c r="T9">
-        <v>0.5980699594343599</v>
+        <v>0.6030323719753022</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>18.99045045894861</v>
+        <v>16.61664415158003</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2202,22 +2202,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07361663749296932</v>
+        <v>0.07346327872385459</v>
       </c>
       <c r="C10">
-        <v>4700.422507324374</v>
+        <v>4670.576817891868</v>
       </c>
       <c r="D10">
-        <v>4771.610507324374</v>
+        <v>4791.250817891868</v>
       </c>
       <c r="E10">
-        <v>379.788</v>
+        <v>429.274</v>
       </c>
       <c r="F10">
-        <v>395.888</v>
+        <v>445.374</v>
       </c>
       <c r="G10">
         <v>324.7</v>
@@ -2238,28 +2238,28 @@
         <v>330.89</v>
       </c>
       <c r="M10">
-        <v>19.9131664</v>
+        <v>22.4023122</v>
       </c>
       <c r="N10">
-        <v>310.9768336</v>
+        <v>308.4876878000001</v>
       </c>
       <c r="O10">
-        <v>77.74420840000001</v>
+        <v>77.12192195000002</v>
       </c>
       <c r="P10">
-        <v>233.2326252</v>
+        <v>231.3657658500001</v>
       </c>
       <c r="Q10">
-        <v>240.4426252</v>
+        <v>238.5757658500001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07673764944887969</v>
+        <v>0.07699783376247757</v>
       </c>
       <c r="T10">
-        <v>0.6030323719753022</v>
+        <v>0.6081038485281333</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2276,7 +2276,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>16.61664415158003</v>
+        <v>14.77035035696003</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2284,22 +2284,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07346327872385459</v>
+        <v>0.07330991995473987</v>
       </c>
       <c r="C11">
-        <v>4670.576817891868</v>
+        <v>4640.89347871966</v>
       </c>
       <c r="D11">
-        <v>4791.250817891868</v>
+        <v>4811.05347871966</v>
       </c>
       <c r="E11">
-        <v>429.274</v>
+        <v>478.76</v>
       </c>
       <c r="F11">
-        <v>445.374</v>
+        <v>494.86</v>
       </c>
       <c r="G11">
         <v>324.7</v>
@@ -2320,28 +2320,28 @@
         <v>330.89</v>
       </c>
       <c r="M11">
-        <v>22.4023122</v>
+        <v>24.891458</v>
       </c>
       <c r="N11">
-        <v>308.4876878000001</v>
+        <v>305.998542</v>
       </c>
       <c r="O11">
-        <v>77.12192195000002</v>
+        <v>76.49963550000001</v>
       </c>
       <c r="P11">
-        <v>231.3657658500001</v>
+        <v>229.4989065</v>
       </c>
       <c r="Q11">
-        <v>238.5757658500001</v>
+        <v>236.7089065</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07699783376247757</v>
+        <v>0.07726379994971097</v>
       </c>
       <c r="T11">
-        <v>0.6081038485281333</v>
+        <v>0.6132880245599162</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2358,7 +2358,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>14.77035035696003</v>
+        <v>13.29331532126403</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2366,22 +2366,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07330991995473987</v>
+        <v>0.07328031118562515</v>
       </c>
       <c r="C12">
-        <v>4640.89347871966</v>
+        <v>4595.24961936512</v>
       </c>
       <c r="D12">
-        <v>4811.05347871966</v>
+        <v>4814.895619365121</v>
       </c>
       <c r="E12">
-        <v>478.76</v>
+        <v>528.246</v>
       </c>
       <c r="F12">
-        <v>494.8600000000001</v>
+        <v>544.346</v>
       </c>
       <c r="G12">
         <v>324.7</v>
@@ -2402,45 +2402,45 @@
         <v>330.89</v>
       </c>
       <c r="M12">
-        <v>24.891458</v>
+        <v>28.1971228</v>
       </c>
       <c r="N12">
-        <v>305.998542</v>
+        <v>302.6928772000001</v>
       </c>
       <c r="O12">
-        <v>76.49963550000001</v>
+        <v>75.67321930000001</v>
       </c>
       <c r="P12">
-        <v>229.4989065</v>
+        <v>227.0196579</v>
       </c>
       <c r="Q12">
-        <v>236.7089065</v>
+        <v>234.2296579</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07726379994971097</v>
+        <v>0.0775357429051968</v>
       </c>
       <c r="T12">
-        <v>0.6132880245599162</v>
+        <v>0.618588698929492</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.29331532126402</v>
+        <v>11.73488523446087</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2448,22 +2448,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07328031118562515</v>
+        <v>0.07313820241651045</v>
       </c>
       <c r="C13">
-        <v>4595.24961936512</v>
+        <v>4564.289902808923</v>
       </c>
       <c r="D13">
-        <v>4814.895619365121</v>
+        <v>4833.421902808924</v>
       </c>
       <c r="E13">
-        <v>528.246</v>
+        <v>577.732</v>
       </c>
       <c r="F13">
-        <v>544.346</v>
+        <v>593.832</v>
       </c>
       <c r="G13">
         <v>324.7</v>
@@ -2484,28 +2484,28 @@
         <v>330.89</v>
       </c>
       <c r="M13">
-        <v>28.1971228</v>
+        <v>30.7604976</v>
       </c>
       <c r="N13">
-        <v>302.6928772000001</v>
+        <v>300.1295024</v>
       </c>
       <c r="O13">
-        <v>75.67321930000001</v>
+        <v>75.03237560000001</v>
       </c>
       <c r="P13">
-        <v>227.0196579</v>
+        <v>225.0971268</v>
       </c>
       <c r="Q13">
-        <v>234.2296579</v>
+        <v>232.3071268</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.0775357429051968</v>
+        <v>0.07781386638239823</v>
       </c>
       <c r="T13">
-        <v>0.618588698929492</v>
+        <v>0.6240098431711035</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2522,7 +2522,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>11.73488523446087</v>
+        <v>10.75697813158913</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2530,22 +2530,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07313820241651045</v>
+        <v>0.07299609364739572</v>
       </c>
       <c r="C14">
-        <v>4564.289902808923</v>
+        <v>4533.47330416305</v>
       </c>
       <c r="D14">
-        <v>4833.421902808924</v>
+        <v>4852.09130416305</v>
       </c>
       <c r="E14">
-        <v>577.732</v>
+        <v>627.2180000000001</v>
       </c>
       <c r="F14">
-        <v>593.832</v>
+        <v>643.3180000000001</v>
       </c>
       <c r="G14">
         <v>324.7</v>
@@ -2566,28 +2566,28 @@
         <v>330.89</v>
       </c>
       <c r="M14">
-        <v>30.7604976</v>
+        <v>33.32387240000001</v>
       </c>
       <c r="N14">
-        <v>300.1295024</v>
+        <v>297.5661276</v>
       </c>
       <c r="O14">
-        <v>75.03237560000001</v>
+        <v>74.3915319</v>
       </c>
       <c r="P14">
-        <v>225.0971268</v>
+        <v>223.1745957</v>
       </c>
       <c r="Q14">
-        <v>232.3071268</v>
+        <v>230.3845957</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07781386638239823</v>
+        <v>0.07809838350275369</v>
       </c>
       <c r="T14">
-        <v>0.6240098431711035</v>
+        <v>0.6295556114182693</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>10.75697813158913</v>
+        <v>9.929518275313045</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2612,22 +2612,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07299609364739572</v>
+        <v>0.073032484878281</v>
       </c>
       <c r="C15">
-        <v>4533.47330416305</v>
+        <v>4479.192717654687</v>
       </c>
       <c r="D15">
-        <v>4852.09130416305</v>
+        <v>4847.296717654687</v>
       </c>
       <c r="E15">
-        <v>627.2180000000001</v>
+        <v>676.7040000000001</v>
       </c>
       <c r="F15">
-        <v>643.3180000000001</v>
+        <v>692.8040000000001</v>
       </c>
       <c r="G15">
         <v>324.7</v>
@@ -2648,45 +2648,45 @@
         <v>330.89</v>
       </c>
       <c r="M15">
-        <v>33.32387240000001</v>
+        <v>37.06501400000001</v>
       </c>
       <c r="N15">
-        <v>297.5661276</v>
+        <v>293.824986</v>
       </c>
       <c r="O15">
-        <v>74.3915319</v>
+        <v>73.45624650000001</v>
       </c>
       <c r="P15">
-        <v>223.1745957</v>
+        <v>220.3687395</v>
       </c>
       <c r="Q15">
-        <v>230.3845957</v>
+        <v>227.5787395</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07809838350275369</v>
+        <v>0.07838951730032674</v>
       </c>
       <c r="T15">
-        <v>0.6295556114182693</v>
+        <v>0.6352303510200205</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>9.929518275313045</v>
+        <v>8.927286524159953</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2694,22 +2694,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.073032484878281</v>
+        <v>0.07290312610916629</v>
       </c>
       <c r="C16">
-        <v>4479.192717654687</v>
+        <v>4446.793059496896</v>
       </c>
       <c r="D16">
-        <v>4847.296717654687</v>
+        <v>4864.383059496896</v>
       </c>
       <c r="E16">
-        <v>676.7040000000001</v>
+        <v>726.1900000000002</v>
       </c>
       <c r="F16">
-        <v>692.8040000000001</v>
+        <v>742.2900000000002</v>
       </c>
       <c r="G16">
         <v>324.7</v>
@@ -2730,28 +2730,28 @@
         <v>330.89</v>
       </c>
       <c r="M16">
-        <v>37.06501400000001</v>
+        <v>39.71251500000001</v>
       </c>
       <c r="N16">
-        <v>293.824986</v>
+        <v>291.177485</v>
       </c>
       <c r="O16">
-        <v>73.45624650000001</v>
+        <v>72.79437125000001</v>
       </c>
       <c r="P16">
-        <v>220.3687395</v>
+        <v>218.38311375</v>
       </c>
       <c r="Q16">
-        <v>227.5787395</v>
+        <v>225.59311375</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07838951730032674</v>
+        <v>0.07868750130490151</v>
       </c>
       <c r="T16">
-        <v>0.6352303510200205</v>
+        <v>0.6410386139065186</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.927286524159953</v>
+        <v>8.332134089215955</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2776,22 +2776,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07290312610916629</v>
+        <v>0.07277376734005156</v>
       </c>
       <c r="C17">
-        <v>4446.793059496896</v>
+        <v>4414.514283476669</v>
       </c>
       <c r="D17">
-        <v>4864.383059496896</v>
+        <v>4881.590283476669</v>
       </c>
       <c r="E17">
-        <v>726.1900000000001</v>
+        <v>775.676</v>
       </c>
       <c r="F17">
-        <v>742.2900000000001</v>
+        <v>791.7760000000001</v>
       </c>
       <c r="G17">
         <v>324.7</v>
@@ -2812,28 +2812,28 @@
         <v>330.89</v>
       </c>
       <c r="M17">
-        <v>39.712515</v>
+        <v>42.360016</v>
       </c>
       <c r="N17">
-        <v>291.177485</v>
+        <v>288.529984</v>
       </c>
       <c r="O17">
-        <v>72.79437125000001</v>
+        <v>72.132496</v>
       </c>
       <c r="P17">
-        <v>218.38311375</v>
+        <v>216.397488</v>
       </c>
       <c r="Q17">
-        <v>225.59311375</v>
+        <v>223.607488</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07868750130490151</v>
+        <v>0.07899258016672805</v>
       </c>
       <c r="T17">
-        <v>0.6410386139065186</v>
+        <v>0.6469851687665049</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2850,7 +2850,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.332134089215957</v>
+        <v>7.811375708639959</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2858,22 +2858,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07277376734005156</v>
+        <v>0.07274640857093687</v>
       </c>
       <c r="C18">
-        <v>4414.514283476669</v>
+        <v>4368.683137918857</v>
       </c>
       <c r="D18">
-        <v>4881.590283476669</v>
+        <v>4885.245137918858</v>
       </c>
       <c r="E18">
-        <v>775.676</v>
+        <v>825.1620000000001</v>
       </c>
       <c r="F18">
-        <v>791.7760000000001</v>
+        <v>841.2620000000002</v>
       </c>
       <c r="G18">
         <v>324.7</v>
@@ -2894,45 +2894,45 @@
         <v>330.89</v>
       </c>
       <c r="M18">
-        <v>42.360016</v>
+        <v>45.68052660000001</v>
       </c>
       <c r="N18">
-        <v>288.529984</v>
+        <v>285.2094734</v>
       </c>
       <c r="O18">
-        <v>72.132496</v>
+        <v>71.30236835000001</v>
       </c>
       <c r="P18">
-        <v>216.397488</v>
+        <v>213.90710505</v>
       </c>
       <c r="Q18">
-        <v>223.607488</v>
+        <v>221.11710505</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07899258016672805</v>
+        <v>0.07930501032642995</v>
       </c>
       <c r="T18">
-        <v>0.6469851687665049</v>
+        <v>0.6530750141050452</v>
       </c>
       <c r="U18">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y18">
-        <v>7.811375708639959</v>
+        <v>7.243567984612507</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2940,22 +2940,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07274640857093687</v>
+        <v>0.07262304980182213</v>
       </c>
       <c r="C19">
-        <v>4368.683137918857</v>
+        <v>4335.744820588341</v>
       </c>
       <c r="D19">
-        <v>4885.245137918858</v>
+        <v>4901.792820588342</v>
       </c>
       <c r="E19">
-        <v>825.1620000000001</v>
+        <v>874.6480000000001</v>
       </c>
       <c r="F19">
-        <v>841.2620000000002</v>
+        <v>890.7480000000002</v>
       </c>
       <c r="G19">
         <v>324.7</v>
@@ -2976,28 +2976,28 @@
         <v>330.89</v>
       </c>
       <c r="M19">
-        <v>45.68052660000001</v>
+        <v>48.36761640000001</v>
       </c>
       <c r="N19">
-        <v>285.2094734</v>
+        <v>282.5223836</v>
       </c>
       <c r="O19">
-        <v>71.30236835000001</v>
+        <v>70.6305959</v>
       </c>
       <c r="P19">
-        <v>213.90710505</v>
+        <v>211.8917877</v>
       </c>
       <c r="Q19">
-        <v>221.11710505</v>
+        <v>219.1017877</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07930501032642995</v>
+        <v>0.07962506073392943</v>
       </c>
       <c r="T19">
-        <v>0.6530750141050452</v>
+        <v>0.6593133922567204</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -3014,7 +3014,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>7.243567984612507</v>
+        <v>6.841147541022922</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3022,22 +3022,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07262304980182215</v>
+        <v>0.07249969103270741</v>
       </c>
       <c r="C20">
-        <v>4335.744820588341</v>
+        <v>4302.918987471209</v>
       </c>
       <c r="D20">
-        <v>4901.792820588341</v>
+        <v>4918.45298747121</v>
       </c>
       <c r="E20">
-        <v>874.648</v>
+        <v>924.134</v>
       </c>
       <c r="F20">
-        <v>890.748</v>
+        <v>940.234</v>
       </c>
       <c r="G20">
         <v>324.7</v>
@@ -3058,28 +3058,28 @@
         <v>330.89</v>
       </c>
       <c r="M20">
-        <v>48.3676164</v>
+        <v>51.05470620000001</v>
       </c>
       <c r="N20">
-        <v>282.5223836</v>
+        <v>279.8352938</v>
       </c>
       <c r="O20">
-        <v>70.6305959</v>
+        <v>69.95882345000001</v>
       </c>
       <c r="P20">
-        <v>211.8917877</v>
+        <v>209.87647035</v>
       </c>
       <c r="Q20">
-        <v>219.1017877</v>
+        <v>217.08647035</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07962506073392943</v>
+        <v>0.07995301362062643</v>
       </c>
       <c r="T20">
-        <v>0.6593133922567204</v>
+        <v>0.6657058044368321</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -3096,7 +3096,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>6.841147541022923</v>
+        <v>6.48108714412698</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3104,22 +3104,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07249969103270741</v>
+        <v>0.0723763322635927</v>
       </c>
       <c r="C21">
-        <v>4302.918987471209</v>
+        <v>4270.206789409759</v>
       </c>
       <c r="D21">
-        <v>4918.45298747121</v>
+        <v>4935.226789409759</v>
       </c>
       <c r="E21">
-        <v>924.134</v>
+        <v>973.6200000000001</v>
       </c>
       <c r="F21">
-        <v>940.234</v>
+        <v>989.7200000000001</v>
       </c>
       <c r="G21">
         <v>324.7</v>
@@ -3140,28 +3140,28 @@
         <v>330.89</v>
       </c>
       <c r="M21">
-        <v>51.05470620000001</v>
+        <v>53.74179600000001</v>
       </c>
       <c r="N21">
-        <v>279.8352938</v>
+        <v>277.148204</v>
       </c>
       <c r="O21">
-        <v>69.95882345000001</v>
+        <v>69.28705100000001</v>
       </c>
       <c r="P21">
-        <v>209.87647035</v>
+        <v>207.861153</v>
       </c>
       <c r="Q21">
-        <v>217.08647035</v>
+        <v>215.071153</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07995301362062643</v>
+        <v>0.08028916532949087</v>
       </c>
       <c r="T21">
-        <v>0.6657058044368321</v>
+        <v>0.6722580269214465</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3178,7 +3178,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.48108714412698</v>
+        <v>6.15703278692063</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3186,22 +3186,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.0723763322635927</v>
+        <v>0.07241047349447799</v>
       </c>
       <c r="C22">
-        <v>4270.206789409759</v>
+        <v>4216.066970029177</v>
       </c>
       <c r="D22">
-        <v>4935.226789409759</v>
+        <v>4930.572970029178</v>
       </c>
       <c r="E22">
-        <v>973.6200000000001</v>
+        <v>1023.106</v>
       </c>
       <c r="F22">
-        <v>989.7200000000001</v>
+        <v>1039.206</v>
       </c>
       <c r="G22">
         <v>324.7</v>
@@ -3222,45 +3222,45 @@
         <v>330.89</v>
       </c>
       <c r="M22">
-        <v>53.74179600000001</v>
+        <v>57.46809180000001</v>
       </c>
       <c r="N22">
-        <v>277.148204</v>
+        <v>273.4219082</v>
       </c>
       <c r="O22">
-        <v>69.28705100000001</v>
+        <v>68.35547705</v>
       </c>
       <c r="P22">
-        <v>207.861153</v>
+        <v>205.06643115</v>
       </c>
       <c r="Q22">
-        <v>215.071153</v>
+        <v>212.27643115</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08028916532949087</v>
+        <v>0.08063382720819998</v>
       </c>
       <c r="T22">
-        <v>0.6722580269214465</v>
+        <v>0.6789761284563044</v>
       </c>
       <c r="U22">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V22">
         <v>0.25</v>
       </c>
       <c r="W22">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y22">
-        <v>6.15703278692063</v>
+        <v>5.757803846203224</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3268,22 +3268,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07241047349447799</v>
+        <v>0.07229461472536326</v>
       </c>
       <c r="C23">
-        <v>4216.066970029177</v>
+        <v>4182.409533900359</v>
       </c>
       <c r="D23">
-        <v>4930.572970029178</v>
+        <v>4946.401533900359</v>
       </c>
       <c r="E23">
-        <v>1023.106</v>
+        <v>1072.592</v>
       </c>
       <c r="F23">
-        <v>1039.206</v>
+        <v>1088.692</v>
       </c>
       <c r="G23">
         <v>324.7</v>
@@ -3304,28 +3304,28 @@
         <v>330.89</v>
       </c>
       <c r="M23">
-        <v>57.46809180000001</v>
+        <v>60.2046676</v>
       </c>
       <c r="N23">
-        <v>273.4219082</v>
+        <v>270.6853324</v>
       </c>
       <c r="O23">
-        <v>68.35547705</v>
+        <v>67.67133310000001</v>
       </c>
       <c r="P23">
-        <v>205.06643115</v>
+        <v>203.0139993</v>
       </c>
       <c r="Q23">
-        <v>212.27643115</v>
+        <v>210.2239993</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08063382720819998</v>
+        <v>0.08098732657097854</v>
       </c>
       <c r="T23">
-        <v>0.6789761284563044</v>
+        <v>0.6858664890048766</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3342,7 +3342,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.757803846203224</v>
+        <v>5.496085489557625</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3350,22 +3350,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07229461472536326</v>
+        <v>0.07217875595624854</v>
       </c>
       <c r="C24">
-        <v>4182.409533900359</v>
+        <v>4148.854053606276</v>
       </c>
       <c r="D24">
-        <v>4946.401533900359</v>
+        <v>4962.332053606277</v>
       </c>
       <c r="E24">
-        <v>1072.592</v>
+        <v>1122.078</v>
       </c>
       <c r="F24">
-        <v>1088.692</v>
+        <v>1138.178</v>
       </c>
       <c r="G24">
         <v>324.7</v>
@@ -3386,28 +3386,28 @@
         <v>330.89</v>
       </c>
       <c r="M24">
-        <v>60.2046676</v>
+        <v>62.94124340000001</v>
       </c>
       <c r="N24">
-        <v>270.6853324</v>
+        <v>267.9487566</v>
       </c>
       <c r="O24">
-        <v>67.67133310000001</v>
+        <v>66.98718915000001</v>
       </c>
       <c r="P24">
-        <v>203.0139993</v>
+        <v>200.96156745</v>
       </c>
       <c r="Q24">
-        <v>210.2239993</v>
+        <v>208.17156745</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08098732657097854</v>
+        <v>0.08135000773538771</v>
       </c>
       <c r="T24">
-        <v>0.6858664890048766</v>
+        <v>0.6929358199573078</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3424,7 +3424,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.496085489557625</v>
+        <v>5.257125250881205</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3432,22 +3432,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07217875595624854</v>
+        <v>0.07206289718713384</v>
       </c>
       <c r="C25">
-        <v>4148.854053606276</v>
+        <v>4115.401517415246</v>
       </c>
       <c r="D25">
-        <v>4962.332053606277</v>
+        <v>4978.365517415246</v>
       </c>
       <c r="E25">
-        <v>1122.078</v>
+        <v>1171.564</v>
       </c>
       <c r="F25">
-        <v>1138.178</v>
+        <v>1187.664</v>
       </c>
       <c r="G25">
         <v>324.7</v>
@@ -3468,28 +3468,28 @@
         <v>330.89</v>
       </c>
       <c r="M25">
-        <v>62.94124340000001</v>
+        <v>65.67781920000002</v>
       </c>
       <c r="N25">
-        <v>267.9487566</v>
+        <v>265.2121808000001</v>
       </c>
       <c r="O25">
-        <v>66.98718915000001</v>
+        <v>66.30304520000001</v>
       </c>
       <c r="P25">
-        <v>200.96156745</v>
+        <v>198.9091356</v>
       </c>
       <c r="Q25">
-        <v>208.17156745</v>
+        <v>206.1191356</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08135000773538771</v>
+        <v>0.08172223314096556</v>
       </c>
       <c r="T25">
-        <v>0.6929358199573078</v>
+        <v>0.7001911859348031</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.257125250881205</v>
+        <v>5.038078365427822</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3514,22 +3514,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07206289718713384</v>
+        <v>0.0719470384180191</v>
       </c>
       <c r="C26">
-        <v>4115.401517415246</v>
+        <v>4082.052926409514</v>
       </c>
       <c r="D26">
-        <v>4978.365517415246</v>
+        <v>4994.502926409515</v>
       </c>
       <c r="E26">
-        <v>1171.564</v>
+        <v>1221.05</v>
       </c>
       <c r="F26">
-        <v>1187.664</v>
+        <v>1237.15</v>
       </c>
       <c r="G26">
         <v>324.7</v>
@@ -3550,28 +3550,28 @@
         <v>330.89</v>
       </c>
       <c r="M26">
-        <v>65.6778192</v>
+        <v>68.41439500000001</v>
       </c>
       <c r="N26">
-        <v>265.2121808000001</v>
+        <v>262.475605</v>
       </c>
       <c r="O26">
-        <v>66.30304520000001</v>
+        <v>65.61890125000001</v>
       </c>
       <c r="P26">
-        <v>198.9091356</v>
+        <v>196.85670375</v>
       </c>
       <c r="Q26">
-        <v>206.1191356</v>
+        <v>204.06670375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08172223314096556</v>
+        <v>0.0821043845573588</v>
       </c>
       <c r="T26">
-        <v>0.7001911859348031</v>
+        <v>0.7076400283383648</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3588,7 +3588,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.038078365427823</v>
+        <v>4.836555230810708</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3596,22 +3596,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.0719470384180191</v>
+        <v>0.0718311796489044</v>
       </c>
       <c r="C27">
-        <v>4082.052926409514</v>
+        <v>4048.809294693579</v>
       </c>
       <c r="D27">
-        <v>4994.502926409515</v>
+        <v>5010.74529469358</v>
       </c>
       <c r="E27">
-        <v>1221.05</v>
+        <v>1270.536</v>
       </c>
       <c r="F27">
-        <v>1237.15</v>
+        <v>1286.636</v>
       </c>
       <c r="G27">
         <v>324.7</v>
@@ -3632,28 +3632,28 @@
         <v>330.89</v>
       </c>
       <c r="M27">
-        <v>68.41439500000001</v>
+        <v>71.15097080000001</v>
       </c>
       <c r="N27">
-        <v>262.475605</v>
+        <v>259.7390292</v>
       </c>
       <c r="O27">
-        <v>65.61890125000001</v>
+        <v>64.9347573</v>
       </c>
       <c r="P27">
-        <v>196.85670375</v>
+        <v>194.8042719</v>
       </c>
       <c r="Q27">
-        <v>204.06670375</v>
+        <v>202.0142719</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.0821043845573588</v>
+        <v>0.08249686439041135</v>
       </c>
       <c r="T27">
-        <v>0.7076400283383648</v>
+        <v>0.7152901908068877</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3670,7 +3670,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.836555230810708</v>
+        <v>4.650533875779527</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3678,22 +3678,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0718311796489044</v>
+        <v>0.07222157087978967</v>
       </c>
       <c r="C28">
-        <v>4048.809294693579</v>
+        <v>3945.011084987297</v>
       </c>
       <c r="D28">
-        <v>5010.74529469358</v>
+        <v>4956.433084987298</v>
       </c>
       <c r="E28">
-        <v>1270.536</v>
+        <v>1320.022</v>
       </c>
       <c r="F28">
-        <v>1286.636</v>
+        <v>1336.122</v>
       </c>
       <c r="G28">
         <v>324.7</v>
@@ -3714,45 +3714,45 @@
         <v>330.89</v>
       </c>
       <c r="M28">
-        <v>71.15097080000001</v>
+        <v>77.22785160000002</v>
       </c>
       <c r="N28">
-        <v>259.7390292</v>
+        <v>253.6621484</v>
       </c>
       <c r="O28">
-        <v>64.9347573</v>
+        <v>63.41553710000001</v>
       </c>
       <c r="P28">
-        <v>194.8042719</v>
+        <v>190.2466113</v>
       </c>
       <c r="Q28">
-        <v>202.0142719</v>
+        <v>197.4566113</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08249686439041135</v>
+        <v>0.08290009709560228</v>
       </c>
       <c r="T28">
-        <v>0.7152901908068877</v>
+        <v>0.7231499467676988</v>
       </c>
       <c r="U28">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V28">
         <v>0.25</v>
       </c>
       <c r="W28">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.650533875779527</v>
+        <v>4.284594134689097</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07222157087978967</v>
+        <v>0.07212446211067496</v>
       </c>
       <c r="C29">
-        <v>3945.011084987297</v>
+        <v>3908.924792479898</v>
       </c>
       <c r="D29">
-        <v>4956.433084987298</v>
+        <v>4969.832792479899</v>
       </c>
       <c r="E29">
-        <v>1320.022</v>
+        <v>1369.508</v>
       </c>
       <c r="F29">
-        <v>1336.122</v>
+        <v>1385.608</v>
       </c>
       <c r="G29">
         <v>324.7</v>
@@ -3796,28 +3796,28 @@
         <v>330.89</v>
       </c>
       <c r="M29">
-        <v>77.22785160000002</v>
+        <v>80.08814240000001</v>
       </c>
       <c r="N29">
-        <v>253.6621484</v>
+        <v>250.8018576</v>
       </c>
       <c r="O29">
-        <v>63.41553710000001</v>
+        <v>62.70046440000001</v>
       </c>
       <c r="P29">
-        <v>190.2466113</v>
+        <v>188.1013932</v>
       </c>
       <c r="Q29">
-        <v>197.4566113</v>
+        <v>195.3113932</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08290009709560228</v>
+        <v>0.08331453070927078</v>
       </c>
       <c r="T29">
-        <v>0.7231499467676988</v>
+        <v>0.731228029282977</v>
       </c>
       <c r="U29">
         <v>0.0578</v>
@@ -3834,7 +3834,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.284594134689097</v>
+        <v>4.131572915593058</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3842,22 +3842,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07212446211067496</v>
+        <v>0.07278860334156023</v>
       </c>
       <c r="C30">
-        <v>3908.924792479898</v>
+        <v>3769.216629860839</v>
       </c>
       <c r="D30">
-        <v>4969.832792479899</v>
+        <v>4879.610629860839</v>
       </c>
       <c r="E30">
-        <v>1369.508</v>
+        <v>1418.994</v>
       </c>
       <c r="F30">
-        <v>1385.608</v>
+        <v>1435.094</v>
       </c>
       <c r="G30">
         <v>324.7</v>
@@ -3878,45 +3878,45 @@
         <v>330.89</v>
       </c>
       <c r="M30">
-        <v>80.08814240000001</v>
+        <v>87.97126220000001</v>
       </c>
       <c r="N30">
-        <v>250.8018576</v>
+        <v>242.9187378</v>
       </c>
       <c r="O30">
-        <v>62.70046440000001</v>
+        <v>60.72968445000001</v>
       </c>
       <c r="P30">
-        <v>188.1013932</v>
+        <v>182.18905335</v>
       </c>
       <c r="Q30">
-        <v>195.3113932</v>
+        <v>189.39905335</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08331453070927078</v>
+        <v>0.08374063850923977</v>
       </c>
       <c r="T30">
-        <v>0.731228029282977</v>
+        <v>0.7395336634184038</v>
       </c>
       <c r="U30">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V30">
         <v>0.25</v>
       </c>
       <c r="W30">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.131572915593058</v>
+        <v>3.761341962420996</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3924,22 +3924,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07278860334156023</v>
+        <v>0.07271774457244551</v>
       </c>
       <c r="C31">
-        <v>3769.216629860839</v>
+        <v>3729.200233055931</v>
       </c>
       <c r="D31">
-        <v>4879.610629860839</v>
+        <v>4889.080233055931</v>
       </c>
       <c r="E31">
-        <v>1418.994</v>
+        <v>1468.48</v>
       </c>
       <c r="F31">
-        <v>1435.094</v>
+        <v>1484.58</v>
       </c>
       <c r="G31">
         <v>324.7</v>
@@ -3960,28 +3960,28 @@
         <v>330.89</v>
       </c>
       <c r="M31">
-        <v>87.9712622</v>
+        <v>91.00475400000001</v>
       </c>
       <c r="N31">
-        <v>242.9187378</v>
+        <v>239.8852460000001</v>
       </c>
       <c r="O31">
-        <v>60.72968445000001</v>
+        <v>59.97131150000001</v>
       </c>
       <c r="P31">
-        <v>182.18905335</v>
+        <v>179.9139345</v>
       </c>
       <c r="Q31">
-        <v>189.39905335</v>
+        <v>187.1239345</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08374063850923977</v>
+        <v>0.08417892081777931</v>
       </c>
       <c r="T31">
-        <v>0.7395336634184038</v>
+        <v>0.7480766013862713</v>
       </c>
       <c r="U31">
         <v>0.0613</v>
@@ -3998,7 +3998,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.761341962420996</v>
+        <v>3.635963897006963</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4006,22 +4006,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07271774457244551</v>
+        <v>0.07264688580333079</v>
       </c>
       <c r="C32">
-        <v>3729.200233055931</v>
+        <v>3689.220662036632</v>
       </c>
       <c r="D32">
-        <v>4889.080233055931</v>
+        <v>4898.586662036632</v>
       </c>
       <c r="E32">
-        <v>1468.48</v>
+        <v>1517.966</v>
       </c>
       <c r="F32">
-        <v>1484.58</v>
+        <v>1534.066</v>
       </c>
       <c r="G32">
         <v>324.7</v>
@@ -4042,28 +4042,28 @@
         <v>330.89</v>
       </c>
       <c r="M32">
-        <v>91.00475400000001</v>
+        <v>94.0382458</v>
       </c>
       <c r="N32">
-        <v>239.8852460000001</v>
+        <v>236.8517542</v>
       </c>
       <c r="O32">
-        <v>59.97131150000001</v>
+        <v>59.21293855000001</v>
       </c>
       <c r="P32">
-        <v>179.9139345</v>
+        <v>177.63881565</v>
       </c>
       <c r="Q32">
-        <v>187.1239345</v>
+        <v>184.84881565</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08417892081777931</v>
+        <v>0.08462990696134898</v>
       </c>
       <c r="T32">
-        <v>0.7480766013862713</v>
+        <v>0.7568671607445119</v>
       </c>
       <c r="U32">
         <v>0.0613</v>
@@ -4080,7 +4080,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.635963897006963</v>
+        <v>3.518674739038997</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4088,22 +4088,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07264688580333079</v>
+        <v>0.0732480270342161</v>
       </c>
       <c r="C33">
-        <v>3689.220662036632</v>
+        <v>3560.23992688171</v>
       </c>
       <c r="D33">
-        <v>4898.586662036632</v>
+        <v>4819.091926881711</v>
       </c>
       <c r="E33">
-        <v>1517.966</v>
+        <v>1567.452</v>
       </c>
       <c r="F33">
-        <v>1534.066</v>
+        <v>1583.552</v>
       </c>
       <c r="G33">
         <v>324.7</v>
@@ -4124,45 +4124,45 @@
         <v>330.89</v>
       </c>
       <c r="M33">
-        <v>94.0382458</v>
+        <v>101.5056832</v>
       </c>
       <c r="N33">
-        <v>236.8517542</v>
+        <v>229.3843168</v>
       </c>
       <c r="O33">
-        <v>59.21293855000001</v>
+        <v>57.34607920000001</v>
       </c>
       <c r="P33">
-        <v>177.63881565</v>
+        <v>172.0382376</v>
       </c>
       <c r="Q33">
-        <v>184.84881565</v>
+        <v>179.2482376</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08462990696134898</v>
+        <v>0.08509415740325896</v>
       </c>
       <c r="T33">
-        <v>0.7568671607445119</v>
+        <v>0.7659162659662302</v>
       </c>
       <c r="U33">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V33">
         <v>0.25</v>
       </c>
       <c r="W33">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.518674739038997</v>
+        <v>3.259817475914491</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4170,22 +4170,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0732480270342161</v>
+        <v>0.07319816826510137</v>
       </c>
       <c r="C34">
-        <v>3560.23992688171</v>
+        <v>3517.248980725448</v>
       </c>
       <c r="D34">
-        <v>4819.091926881711</v>
+        <v>4825.586980725448</v>
       </c>
       <c r="E34">
-        <v>1567.452</v>
+        <v>1616.938</v>
       </c>
       <c r="F34">
-        <v>1583.552</v>
+        <v>1633.038</v>
       </c>
       <c r="G34">
         <v>324.7</v>
@@ -4206,28 +4206,28 @@
         <v>330.89</v>
       </c>
       <c r="M34">
-        <v>101.5056832</v>
+        <v>104.6777358</v>
       </c>
       <c r="N34">
-        <v>229.3843168</v>
+        <v>226.2122642</v>
       </c>
       <c r="O34">
-        <v>57.34607920000001</v>
+        <v>56.55306605000001</v>
       </c>
       <c r="P34">
-        <v>172.0382376</v>
+        <v>169.65919815</v>
       </c>
       <c r="Q34">
-        <v>179.2482376</v>
+        <v>176.86919815</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08509415740325896</v>
+        <v>0.08557226606731547</v>
       </c>
       <c r="T34">
-        <v>0.7659162659662302</v>
+        <v>0.7752354937318803</v>
       </c>
       <c r="U34">
         <v>0.0641</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>3.259817475914491</v>
+        <v>3.161035128159507</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4252,22 +4252,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07319816826510137</v>
+        <v>0.07314830949598664</v>
       </c>
       <c r="C35">
-        <v>3517.248980725448</v>
+        <v>3474.275565945924</v>
       </c>
       <c r="D35">
-        <v>4825.586980725448</v>
+        <v>4832.099565945925</v>
       </c>
       <c r="E35">
-        <v>1616.938</v>
+        <v>1666.424</v>
       </c>
       <c r="F35">
-        <v>1633.038</v>
+        <v>1682.524</v>
       </c>
       <c r="G35">
         <v>324.7</v>
@@ -4288,28 +4288,28 @@
         <v>330.89</v>
       </c>
       <c r="M35">
-        <v>104.6777358</v>
+        <v>107.8497884</v>
       </c>
       <c r="N35">
-        <v>226.2122642</v>
+        <v>223.0402116</v>
       </c>
       <c r="O35">
-        <v>56.55306605000001</v>
+        <v>55.76005290000001</v>
       </c>
       <c r="P35">
-        <v>169.65919815</v>
+        <v>167.2801587</v>
       </c>
       <c r="Q35">
-        <v>176.86919815</v>
+        <v>174.4901587</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08557226606731547</v>
+        <v>0.08606486287270704</v>
       </c>
       <c r="T35">
-        <v>0.7752354937318803</v>
+        <v>0.7848371223389137</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.161035128159507</v>
+        <v>3.068063506743051</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4334,22 +4334,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07314830949598664</v>
+        <v>0.07514595072687193</v>
       </c>
       <c r="C36">
-        <v>3474.275565945924</v>
+        <v>3176.907868585584</v>
       </c>
       <c r="D36">
-        <v>4832.099565945925</v>
+        <v>4584.217868585584</v>
       </c>
       <c r="E36">
-        <v>1666.424</v>
+        <v>1715.91</v>
       </c>
       <c r="F36">
-        <v>1682.524</v>
+        <v>1732.01</v>
       </c>
       <c r="G36">
         <v>324.7</v>
@@ -4370,45 +4370,45 @@
         <v>330.89</v>
       </c>
       <c r="M36">
-        <v>107.8497884</v>
+        <v>124.531519</v>
       </c>
       <c r="N36">
-        <v>223.0402116</v>
+        <v>206.358481</v>
       </c>
       <c r="O36">
-        <v>55.76005290000001</v>
+        <v>51.58962025</v>
       </c>
       <c r="P36">
-        <v>167.2801587</v>
+        <v>154.76886075</v>
       </c>
       <c r="Q36">
-        <v>174.4901587</v>
+        <v>161.97886075</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08606486287270704</v>
+        <v>0.0865726165028799</v>
       </c>
       <c r="T36">
-        <v>0.7848371223389137</v>
+        <v>0.7947341856723175</v>
       </c>
       <c r="U36">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V36">
         <v>0.25</v>
       </c>
       <c r="W36">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y36">
-        <v>3.068063506743051</v>
+        <v>2.657078325688776</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4416,22 +4416,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07514595072687193</v>
+        <v>0.0751545919577572</v>
       </c>
       <c r="C37">
-        <v>3176.907868585584</v>
+        <v>3126.40483430602</v>
       </c>
       <c r="D37">
-        <v>4584.217868585584</v>
+        <v>4583.200834306021</v>
       </c>
       <c r="E37">
-        <v>1715.91</v>
+        <v>1765.396</v>
       </c>
       <c r="F37">
-        <v>1732.01</v>
+        <v>1781.496</v>
       </c>
       <c r="G37">
         <v>324.7</v>
@@ -4452,28 +4452,28 @@
         <v>330.89</v>
       </c>
       <c r="M37">
-        <v>124.531519</v>
+        <v>128.0895624</v>
       </c>
       <c r="N37">
-        <v>206.358481</v>
+        <v>202.8004376</v>
       </c>
       <c r="O37">
-        <v>51.58962025</v>
+        <v>50.7001094</v>
       </c>
       <c r="P37">
-        <v>154.76886075</v>
+        <v>152.1003282</v>
       </c>
       <c r="Q37">
-        <v>161.97886075</v>
+        <v>159.3103282</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.0865726165028799</v>
+        <v>0.08709623743399564</v>
       </c>
       <c r="T37">
-        <v>0.7947341856723175</v>
+        <v>0.8049405322348899</v>
       </c>
       <c r="U37">
         <v>0.07190000000000001</v>
@@ -4490,7 +4490,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.657078325688776</v>
+        <v>2.583270594419643</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4498,22 +4498,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0751545919577572</v>
+        <v>0.07516323318864249</v>
       </c>
       <c r="C38">
-        <v>3126.40483430602</v>
+        <v>3075.902251195806</v>
       </c>
       <c r="D38">
-        <v>4583.200834306021</v>
+        <v>4582.184251195807</v>
       </c>
       <c r="E38">
-        <v>1765.396</v>
+        <v>1814.882</v>
       </c>
       <c r="F38">
-        <v>1781.496</v>
+        <v>1830.982</v>
       </c>
       <c r="G38">
         <v>324.7</v>
@@ -4534,28 +4534,28 @@
         <v>330.89</v>
       </c>
       <c r="M38">
-        <v>128.0895624</v>
+        <v>131.6476058</v>
       </c>
       <c r="N38">
-        <v>202.8004376</v>
+        <v>199.2423942</v>
       </c>
       <c r="O38">
-        <v>50.70010940000001</v>
+        <v>49.81059855</v>
       </c>
       <c r="P38">
-        <v>152.1003282</v>
+        <v>149.43179565</v>
       </c>
       <c r="Q38">
-        <v>159.3103282</v>
+        <v>156.64179565</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08709623743399564</v>
+        <v>0.08763648125181348</v>
       </c>
       <c r="T38">
-        <v>0.8049405322348899</v>
+        <v>0.8154708897994489</v>
       </c>
       <c r="U38">
         <v>0.07190000000000001</v>
@@ -4572,7 +4572,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.583270594419644</v>
+        <v>2.513452470246139</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4580,22 +4580,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07516323318864249</v>
+        <v>0.07628337441952777</v>
       </c>
       <c r="C39">
-        <v>3075.902251195806</v>
+        <v>2898.350516757906</v>
       </c>
       <c r="D39">
-        <v>4582.184251195807</v>
+        <v>4454.118516757906</v>
       </c>
       <c r="E39">
-        <v>1814.882</v>
+        <v>1864.368</v>
       </c>
       <c r="F39">
-        <v>1830.982</v>
+        <v>1880.468</v>
       </c>
       <c r="G39">
         <v>324.7</v>
@@ -4616,45 +4616,45 @@
         <v>330.89</v>
       </c>
       <c r="M39">
-        <v>131.6476058</v>
+        <v>142.5394744</v>
       </c>
       <c r="N39">
-        <v>199.2423942</v>
+        <v>188.3505256</v>
       </c>
       <c r="O39">
-        <v>49.81059855</v>
+        <v>47.08763140000001</v>
       </c>
       <c r="P39">
-        <v>149.43179565</v>
+        <v>141.2628942</v>
       </c>
       <c r="Q39">
-        <v>156.64179565</v>
+        <v>148.4728942</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08763648125181348</v>
+        <v>0.08819415228956093</v>
       </c>
       <c r="T39">
-        <v>0.8154708897994489</v>
+        <v>0.8263409363177034</v>
       </c>
       <c r="U39">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y39">
-        <v>2.513452470246139</v>
+        <v>2.321392031174769</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4662,22 +4662,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07628337441952777</v>
+        <v>0.07632126565041306</v>
       </c>
       <c r="C40">
-        <v>2898.350516757906</v>
+        <v>2844.657466533021</v>
       </c>
       <c r="D40">
-        <v>4454.118516757906</v>
+        <v>4449.911466533022</v>
       </c>
       <c r="E40">
-        <v>1864.368</v>
+        <v>1913.854</v>
       </c>
       <c r="F40">
-        <v>1880.468</v>
+        <v>1929.954</v>
       </c>
       <c r="G40">
         <v>324.7</v>
@@ -4698,28 +4698,28 @@
         <v>330.89</v>
       </c>
       <c r="M40">
-        <v>142.5394744</v>
+        <v>146.2905132</v>
       </c>
       <c r="N40">
-        <v>188.3505256</v>
+        <v>184.5994868</v>
       </c>
       <c r="O40">
-        <v>47.08763140000001</v>
+        <v>46.14987170000001</v>
       </c>
       <c r="P40">
-        <v>141.2628942</v>
+        <v>138.4496151</v>
       </c>
       <c r="Q40">
-        <v>148.4728942</v>
+        <v>145.6596151</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08819415228956093</v>
+        <v>0.08877010762362797</v>
       </c>
       <c r="T40">
-        <v>0.8263409363177034</v>
+        <v>0.8375673778037694</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.321392031174769</v>
+        <v>2.261869158580544</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4744,22 +4744,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07632126565041306</v>
+        <v>0.07635915688129834</v>
       </c>
       <c r="C41">
-        <v>2844.657466533021</v>
+        <v>2790.972356182121</v>
       </c>
       <c r="D41">
-        <v>4449.911466533022</v>
+        <v>4445.712356182122</v>
       </c>
       <c r="E41">
-        <v>1913.854</v>
+        <v>1963.34</v>
       </c>
       <c r="F41">
-        <v>1929.954</v>
+        <v>1979.44</v>
       </c>
       <c r="G41">
         <v>324.7</v>
@@ -4780,28 +4780,28 @@
         <v>330.89</v>
       </c>
       <c r="M41">
-        <v>146.2905132</v>
+        <v>150.041552</v>
       </c>
       <c r="N41">
-        <v>184.5994868</v>
+        <v>180.848448</v>
       </c>
       <c r="O41">
-        <v>46.14987170000001</v>
+        <v>45.212112</v>
       </c>
       <c r="P41">
-        <v>138.4496151</v>
+        <v>135.636336</v>
       </c>
       <c r="Q41">
-        <v>145.6596151</v>
+        <v>142.846336</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08877010762362797</v>
+        <v>0.08936526146883056</v>
       </c>
       <c r="T41">
-        <v>0.8375673778037694</v>
+        <v>0.8491680340060377</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.261869158580544</v>
+        <v>2.205322429616031</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4826,22 +4826,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07635915688129834</v>
+        <v>0.07639704811218362</v>
       </c>
       <c r="C42">
-        <v>2790.972356182121</v>
+        <v>2737.295163249272</v>
       </c>
       <c r="D42">
-        <v>4445.712356182122</v>
+        <v>4441.521163249273</v>
       </c>
       <c r="E42">
-        <v>1963.34</v>
+        <v>2012.826</v>
       </c>
       <c r="F42">
-        <v>1979.44</v>
+        <v>2028.926</v>
       </c>
       <c r="G42">
         <v>324.7</v>
@@ -4862,28 +4862,28 @@
         <v>330.89</v>
       </c>
       <c r="M42">
-        <v>150.041552</v>
+        <v>153.7925908000001</v>
       </c>
       <c r="N42">
-        <v>180.848448</v>
+        <v>177.0974092</v>
       </c>
       <c r="O42">
-        <v>45.212112</v>
+        <v>44.2743523</v>
       </c>
       <c r="P42">
-        <v>135.636336</v>
+        <v>132.8230569</v>
       </c>
       <c r="Q42">
-        <v>142.846336</v>
+        <v>140.0330569</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08936526146883056</v>
+        <v>0.08998059002065022</v>
       </c>
       <c r="T42">
-        <v>0.8491680340060377</v>
+        <v>0.8611619327914338</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.205322429616031</v>
+        <v>2.151534077674176</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4908,22 +4908,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07639704811218362</v>
+        <v>0.07643493934306891</v>
       </c>
       <c r="C43">
-        <v>2737.295163249272</v>
+        <v>2683.625865363138</v>
       </c>
       <c r="D43">
-        <v>4441.521163249273</v>
+        <v>4437.337865363138</v>
       </c>
       <c r="E43">
-        <v>2012.826</v>
+        <v>2062.312</v>
       </c>
       <c r="F43">
-        <v>2028.926</v>
+        <v>2078.412</v>
       </c>
       <c r="G43">
         <v>324.7</v>
@@ -4944,28 +4944,28 @@
         <v>330.89</v>
       </c>
       <c r="M43">
-        <v>153.7925908000001</v>
+        <v>157.5436296</v>
       </c>
       <c r="N43">
-        <v>177.0974092</v>
+        <v>173.3463704</v>
       </c>
       <c r="O43">
-        <v>44.2743523</v>
+        <v>43.3365926</v>
       </c>
       <c r="P43">
-        <v>132.8230569</v>
+        <v>130.0097778</v>
       </c>
       <c r="Q43">
-        <v>140.0330569</v>
+        <v>137.2197778</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08998059002065022</v>
+        <v>0.09061713679839467</v>
       </c>
       <c r="T43">
-        <v>0.8611619327914338</v>
+        <v>0.8735694142935676</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4982,7 +4982,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.151534077674176</v>
+        <v>2.100307075824791</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4990,22 +4990,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07643493934306891</v>
+        <v>0.07647283057395418</v>
       </c>
       <c r="C44">
-        <v>2683.625865363138</v>
+        <v>2629.96444023659</v>
       </c>
       <c r="D44">
-        <v>4437.337865363138</v>
+        <v>4433.162440236591</v>
       </c>
       <c r="E44">
-        <v>2062.312</v>
+        <v>2111.798</v>
       </c>
       <c r="F44">
-        <v>2078.412</v>
+        <v>2127.898</v>
       </c>
       <c r="G44">
         <v>324.7</v>
@@ -5026,28 +5026,28 @@
         <v>330.89</v>
       </c>
       <c r="M44">
-        <v>157.5436296</v>
+        <v>161.2946684</v>
       </c>
       <c r="N44">
-        <v>173.3463704</v>
+        <v>169.5953316</v>
       </c>
       <c r="O44">
-        <v>43.3365926</v>
+        <v>42.3988329</v>
       </c>
       <c r="P44">
-        <v>130.0097778</v>
+        <v>127.1964987</v>
       </c>
       <c r="Q44">
-        <v>137.2197778</v>
+        <v>134.4064987</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09061713679839467</v>
+        <v>0.09127601855079681</v>
       </c>
       <c r="T44">
-        <v>0.8735694142935676</v>
+        <v>0.8864122460238464</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -5064,7 +5064,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.100307075824791</v>
+        <v>2.051462725224214</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5072,22 +5072,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07647283057395418</v>
+        <v>0.07651072180483948</v>
       </c>
       <c r="C45">
-        <v>2629.96444023659</v>
+        <v>2576.310865666303</v>
       </c>
       <c r="D45">
-        <v>4433.162440236591</v>
+        <v>4428.994865666303</v>
       </c>
       <c r="E45">
-        <v>2111.798</v>
+        <v>2161.284</v>
       </c>
       <c r="F45">
-        <v>2127.898</v>
+        <v>2177.384</v>
       </c>
       <c r="G45">
         <v>324.7</v>
@@ -5108,28 +5108,28 @@
         <v>330.89</v>
       </c>
       <c r="M45">
-        <v>161.2946684</v>
+        <v>165.0457072</v>
       </c>
       <c r="N45">
-        <v>169.5953316</v>
+        <v>165.8442928</v>
       </c>
       <c r="O45">
-        <v>42.3988329</v>
+        <v>41.46107320000001</v>
       </c>
       <c r="P45">
-        <v>127.1964987</v>
+        <v>124.3832196</v>
       </c>
       <c r="Q45">
-        <v>134.4064987</v>
+        <v>131.5932196</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09127601855079681</v>
+        <v>0.0919584317943562</v>
       </c>
       <c r="T45">
-        <v>0.8864122460238464</v>
+        <v>0.899713750315921</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5146,7 +5146,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.051462725224214</v>
+        <v>2.00483857237821</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5154,22 +5154,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07651072180483948</v>
+        <v>0.08134111303572476</v>
       </c>
       <c r="C46">
-        <v>2576.310865666303</v>
+        <v>2052.843470289529</v>
       </c>
       <c r="D46">
-        <v>4428.994865666303</v>
+        <v>3955.013470289529</v>
       </c>
       <c r="E46">
-        <v>2161.284</v>
+        <v>2210.77</v>
       </c>
       <c r="F46">
-        <v>2177.384</v>
+        <v>2226.87</v>
       </c>
       <c r="G46">
         <v>324.7</v>
@@ -5190,45 +5190,45 @@
         <v>330.89</v>
       </c>
       <c r="M46">
-        <v>165.0457072</v>
+        <v>200.4183</v>
       </c>
       <c r="N46">
-        <v>165.8442928</v>
+        <v>130.4717</v>
       </c>
       <c r="O46">
-        <v>41.46107320000001</v>
+        <v>32.61792500000001</v>
       </c>
       <c r="P46">
-        <v>124.3832196</v>
+        <v>97.85377500000001</v>
       </c>
       <c r="Q46">
-        <v>131.5932196</v>
+        <v>105.063775</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0919584317943562</v>
+        <v>0.09266566006495409</v>
       </c>
       <c r="T46">
-        <v>0.899713750315921</v>
+        <v>0.9134989456731618</v>
       </c>
       <c r="U46">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V46">
         <v>0.25</v>
       </c>
       <c r="W46">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>2.00483857237821</v>
+        <v>1.650996939900199</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5236,22 +5236,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08134111303572476</v>
+        <v>0.08148550426661004</v>
       </c>
       <c r="C47">
-        <v>2052.843470289529</v>
+        <v>1990.745715885977</v>
       </c>
       <c r="D47">
-        <v>3955.013470289529</v>
+        <v>3942.401715885977</v>
       </c>
       <c r="E47">
-        <v>2210.77</v>
+        <v>2260.256</v>
       </c>
       <c r="F47">
-        <v>2226.87</v>
+        <v>2276.356</v>
       </c>
       <c r="G47">
         <v>324.7</v>
@@ -5272,28 +5272,28 @@
         <v>330.89</v>
       </c>
       <c r="M47">
-        <v>200.4183</v>
+        <v>204.87204</v>
       </c>
       <c r="N47">
-        <v>130.4717</v>
+        <v>126.01796</v>
       </c>
       <c r="O47">
-        <v>32.61792500000001</v>
+        <v>31.50449000000001</v>
       </c>
       <c r="P47">
-        <v>97.85377500000001</v>
+        <v>94.51347000000004</v>
       </c>
       <c r="Q47">
-        <v>105.063775</v>
+        <v>101.72347</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09266566006495409</v>
+        <v>0.09339908197520377</v>
       </c>
       <c r="T47">
-        <v>0.9134989456731618</v>
+        <v>0.9277947038214116</v>
       </c>
       <c r="U47">
         <v>0.09</v>
@@ -5310,7 +5310,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>1.650996939900199</v>
+        <v>1.615105702076282</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5318,22 +5318,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08148550426661004</v>
+        <v>0.08162989549749533</v>
       </c>
       <c r="C48">
-        <v>1990.745715885977</v>
+        <v>1928.728138585918</v>
       </c>
       <c r="D48">
-        <v>3942.401715885977</v>
+        <v>3929.870138585919</v>
       </c>
       <c r="E48">
-        <v>2260.256</v>
+        <v>2309.742</v>
       </c>
       <c r="F48">
-        <v>2276.356</v>
+        <v>2325.842</v>
       </c>
       <c r="G48">
         <v>324.7</v>
@@ -5354,28 +5354,28 @@
         <v>330.89</v>
       </c>
       <c r="M48">
-        <v>204.87204</v>
+        <v>209.32578</v>
       </c>
       <c r="N48">
-        <v>126.01796</v>
+        <v>121.56422</v>
       </c>
       <c r="O48">
-        <v>31.50449000000001</v>
+        <v>30.39105500000001</v>
       </c>
       <c r="P48">
-        <v>94.51347000000004</v>
+        <v>91.17316500000003</v>
       </c>
       <c r="Q48">
-        <v>101.72347</v>
+        <v>98.38316500000002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09339908197520377</v>
+        <v>0.09416018018395343</v>
       </c>
       <c r="T48">
-        <v>0.9277947038214116</v>
+        <v>0.9426299245412935</v>
       </c>
       <c r="U48">
         <v>0.09</v>
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>1.615105702076282</v>
+        <v>1.580741750968276</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5400,22 +5400,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08162989549749533</v>
+        <v>0.08177428672838061</v>
       </c>
       <c r="C49">
-        <v>1928.728138585918</v>
+        <v>1866.789976243326</v>
       </c>
       <c r="D49">
-        <v>3929.870138585919</v>
+        <v>3917.417976243326</v>
       </c>
       <c r="E49">
-        <v>2309.742</v>
+        <v>2359.228000000001</v>
       </c>
       <c r="F49">
-        <v>2325.842</v>
+        <v>2375.328</v>
       </c>
       <c r="G49">
         <v>324.7</v>
@@ -5436,28 +5436,28 @@
         <v>330.89</v>
       </c>
       <c r="M49">
-        <v>209.32578</v>
+        <v>213.77952</v>
       </c>
       <c r="N49">
-        <v>121.56422</v>
+        <v>117.11048</v>
       </c>
       <c r="O49">
-        <v>30.39105500000001</v>
+        <v>29.27762000000001</v>
       </c>
       <c r="P49">
-        <v>91.17316500000003</v>
+        <v>87.83286000000001</v>
       </c>
       <c r="Q49">
-        <v>98.38316500000002</v>
+        <v>95.04286</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09416018018395343</v>
+        <v>0.09495055140073191</v>
       </c>
       <c r="T49">
-        <v>0.9426299245412935</v>
+        <v>0.9580357306734785</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5474,7 +5474,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.580741750968276</v>
+        <v>1.547809631156436</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08177428672838059</v>
+        <v>0.08191867795926588</v>
       </c>
       <c r="C50">
-        <v>1866.789976243328</v>
+        <v>1804.930476341382</v>
       </c>
       <c r="D50">
-        <v>3917.417976243327</v>
+        <v>3905.044476341382</v>
       </c>
       <c r="E50">
-        <v>2359.228</v>
+        <v>2408.714</v>
       </c>
       <c r="F50">
-        <v>2375.328</v>
+        <v>2424.814</v>
       </c>
       <c r="G50">
         <v>324.7</v>
@@ -5518,28 +5518,28 @@
         <v>330.89</v>
       </c>
       <c r="M50">
-        <v>213.77952</v>
+        <v>218.23326</v>
       </c>
       <c r="N50">
-        <v>117.1104800000001</v>
+        <v>112.65674</v>
       </c>
       <c r="O50">
-        <v>29.27762000000001</v>
+        <v>28.164185</v>
       </c>
       <c r="P50">
-        <v>87.83286000000004</v>
+        <v>84.49255500000001</v>
       </c>
       <c r="Q50">
-        <v>95.04286000000003</v>
+        <v>91.702555</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09495055140073191</v>
+        <v>0.095771917567188</v>
       </c>
       <c r="T50">
-        <v>0.9580357306734785</v>
+        <v>0.9740456860657492</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5556,7 +5556,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.547809631156436</v>
+        <v>1.516221679500183</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5564,22 +5564,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08191867795926588</v>
+        <v>0.1053199343020529</v>
       </c>
       <c r="C51">
-        <v>1804.930476341382</v>
+        <v>433.2603717038319</v>
       </c>
       <c r="D51">
-        <v>3905.044476341382</v>
+        <v>2582.860371703832</v>
       </c>
       <c r="E51">
-        <v>2408.714</v>
+        <v>2458.2</v>
       </c>
       <c r="F51">
-        <v>2424.814</v>
+        <v>2474.3</v>
       </c>
       <c r="G51">
         <v>324.7</v>
@@ -5600,45 +5600,45 @@
         <v>330.89</v>
       </c>
       <c r="M51">
-        <v>218.23326</v>
+        <v>363.2272400000001</v>
       </c>
       <c r="N51">
-        <v>112.65674</v>
+        <v>-32.33724000000001</v>
       </c>
       <c r="O51">
-        <v>28.164185</v>
+        <v>-8.084310000000002</v>
       </c>
       <c r="P51">
-        <v>84.49255500000001</v>
+        <v>-24.25293000000001</v>
       </c>
       <c r="Q51">
-        <v>91.702555</v>
+        <v>-17.04293000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.095771917567188</v>
+        <v>0.09727255663708484</v>
       </c>
       <c r="T51">
-        <v>0.9740456860657492</v>
+        <v>1.00329593467607</v>
       </c>
       <c r="U51">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.25</v>
+        <v>0.2277431064916827</v>
       </c>
       <c r="W51">
-        <v>0.0675</v>
+        <v>0.113367311967021</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y51">
-        <v>1.516221679500183</v>
+        <v>0.9109724259667309</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5646,22 +5646,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1053199343020529</v>
+        <v>0.1063299343020529</v>
       </c>
       <c r="C52">
-        <v>433.2603717038319</v>
+        <v>346.5738931111018</v>
       </c>
       <c r="D52">
-        <v>2582.860371703832</v>
+        <v>2545.659893111102</v>
       </c>
       <c r="E52">
-        <v>2458.2</v>
+        <v>2507.686</v>
       </c>
       <c r="F52">
-        <v>2474.3</v>
+        <v>2523.786</v>
       </c>
       <c r="G52">
         <v>324.7</v>
@@ -5682,37 +5682,37 @@
         <v>330.89</v>
       </c>
       <c r="M52">
-        <v>363.2272400000001</v>
+        <v>370.4917848000001</v>
       </c>
       <c r="N52">
-        <v>-32.33724000000001</v>
+        <v>-39.60178480000002</v>
       </c>
       <c r="O52">
-        <v>-8.084310000000002</v>
+        <v>-9.900446200000005</v>
       </c>
       <c r="P52">
-        <v>-24.25293000000001</v>
+        <v>-29.70133860000001</v>
       </c>
       <c r="Q52">
-        <v>-17.04293000000001</v>
+        <v>-22.49133860000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09727255663708484</v>
+        <v>0.09832301697661719</v>
       </c>
       <c r="T52">
-        <v>1.00329593467607</v>
+        <v>1.023771361914358</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2277431064916827</v>
+        <v>0.2232775553840027</v>
       </c>
       <c r="W52">
-        <v>0.113367311967021</v>
+        <v>0.1140228548696284</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5720,7 +5720,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.9109724259667309</v>
+        <v>0.8931102215360107</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5728,22 +5728,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1063299343020529</v>
+        <v>0.1073399343020529</v>
       </c>
       <c r="C53">
-        <v>346.5738931111018</v>
+        <v>260.9437835774102</v>
       </c>
       <c r="D53">
-        <v>2545.659893111102</v>
+        <v>2509.515783577411</v>
       </c>
       <c r="E53">
-        <v>2507.686</v>
+        <v>2557.172</v>
       </c>
       <c r="F53">
-        <v>2523.786</v>
+        <v>2573.272</v>
       </c>
       <c r="G53">
         <v>324.7</v>
@@ -5764,37 +5764,37 @@
         <v>330.89</v>
       </c>
       <c r="M53">
-        <v>370.4917848000001</v>
+        <v>377.7563296000001</v>
       </c>
       <c r="N53">
-        <v>-39.60178480000002</v>
+        <v>-46.86632960000003</v>
       </c>
       <c r="O53">
-        <v>-9.900446200000005</v>
+        <v>-11.71658240000001</v>
       </c>
       <c r="P53">
-        <v>-29.70133860000001</v>
+        <v>-35.14974720000002</v>
       </c>
       <c r="Q53">
-        <v>-22.49133860000001</v>
+        <v>-27.93974720000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09832301697661719</v>
+        <v>0.09941724649696337</v>
       </c>
       <c r="T53">
-        <v>1.023771361914358</v>
+        <v>1.04509993195424</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2232775553840027</v>
+        <v>0.2189837562420026</v>
       </c>
       <c r="W53">
-        <v>0.1140228548696284</v>
+        <v>0.114653184583674</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8931102215360107</v>
+        <v>0.8759350249680105</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5810,22 +5810,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1073399343020529</v>
+        <v>0.1083499343020529</v>
       </c>
       <c r="C54">
-        <v>260.9437835774102</v>
+        <v>176.3256770095873</v>
       </c>
       <c r="D54">
-        <v>2509.515783577411</v>
+        <v>2474.383677009588</v>
       </c>
       <c r="E54">
-        <v>2557.172</v>
+        <v>2606.658</v>
       </c>
       <c r="F54">
-        <v>2573.272</v>
+        <v>2622.758</v>
       </c>
       <c r="G54">
         <v>324.7</v>
@@ -5846,37 +5846,37 @@
         <v>330.89</v>
       </c>
       <c r="M54">
-        <v>377.7563296000001</v>
+        <v>385.0208744000001</v>
       </c>
       <c r="N54">
-        <v>-46.86632960000003</v>
+        <v>-54.13087440000004</v>
       </c>
       <c r="O54">
-        <v>-11.71658240000001</v>
+        <v>-13.53271860000001</v>
       </c>
       <c r="P54">
-        <v>-35.14974720000002</v>
+        <v>-40.59815580000003</v>
       </c>
       <c r="Q54">
-        <v>-27.93974720000002</v>
+        <v>-33.38815580000003</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.09941724649696337</v>
+        <v>0.1005580389756222</v>
       </c>
       <c r="T54">
-        <v>1.04509993195424</v>
+        <v>1.067336100719224</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.2189837562420026</v>
+        <v>0.2148519872563044</v>
       </c>
       <c r="W54">
-        <v>0.114653184583674</v>
+        <v>0.1152597282707745</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.8759350249680105</v>
+        <v>0.8594079490252178</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5892,22 +5892,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1083499343020529</v>
+        <v>0.1093599343020529</v>
       </c>
       <c r="C55">
-        <v>176.3256770095873</v>
+        <v>92.67765743625523</v>
       </c>
       <c r="D55">
-        <v>2474.383677009588</v>
+        <v>2440.221657436256</v>
       </c>
       <c r="E55">
-        <v>2606.658</v>
+        <v>2656.144000000001</v>
       </c>
       <c r="F55">
-        <v>2622.758</v>
+        <v>2672.244000000001</v>
       </c>
       <c r="G55">
         <v>324.7</v>
@@ -5928,37 +5928,37 @@
         <v>330.89</v>
       </c>
       <c r="M55">
-        <v>385.0208744000001</v>
+        <v>392.2854192000001</v>
       </c>
       <c r="N55">
-        <v>-54.13087440000004</v>
+        <v>-61.39541920000011</v>
       </c>
       <c r="O55">
-        <v>-13.53271860000001</v>
+        <v>-15.34885480000003</v>
       </c>
       <c r="P55">
-        <v>-40.59815580000003</v>
+        <v>-46.04656440000008</v>
       </c>
       <c r="Q55">
-        <v>-33.38815580000003</v>
+        <v>-38.83656440000008</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1005580389756222</v>
+        <v>0.1017484311272661</v>
       </c>
       <c r="T55">
-        <v>1.067336100719224</v>
+        <v>1.090539059430511</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.2148519872563044</v>
+        <v>0.210873246751558</v>
       </c>
       <c r="W55">
-        <v>0.1152597282707745</v>
+        <v>0.1158438073768713</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5966,7 +5966,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8594079490252178</v>
+        <v>0.8434929870062321</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5974,22 +5974,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1093599343020529</v>
+        <v>0.1103699343020529</v>
       </c>
       <c r="C56">
-        <v>92.67765743625523</v>
+        <v>9.960092175888349</v>
       </c>
       <c r="D56">
-        <v>2440.221657436256</v>
+        <v>2406.990092175889</v>
       </c>
       <c r="E56">
-        <v>2656.144000000001</v>
+        <v>2705.630000000001</v>
       </c>
       <c r="F56">
-        <v>2672.244000000001</v>
+        <v>2721.73</v>
       </c>
       <c r="G56">
         <v>324.7</v>
@@ -6010,37 +6010,37 @@
         <v>330.89</v>
       </c>
       <c r="M56">
-        <v>392.2854192000001</v>
+        <v>399.5499640000001</v>
       </c>
       <c r="N56">
-        <v>-61.39541920000011</v>
+        <v>-68.65996400000006</v>
       </c>
       <c r="O56">
-        <v>-15.34885480000003</v>
+        <v>-17.16499100000001</v>
       </c>
       <c r="P56">
-        <v>-46.04656440000008</v>
+        <v>-51.49497300000004</v>
       </c>
       <c r="Q56">
-        <v>-38.83656440000008</v>
+        <v>-44.28497300000004</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1017484311272661</v>
+        <v>0.1029917295967609</v>
       </c>
       <c r="T56">
-        <v>1.090539059430511</v>
+        <v>1.114773260751189</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.210873246751558</v>
+        <v>0.2070391877197116</v>
       </c>
       <c r="W56">
-        <v>0.1158438073768713</v>
+        <v>0.1164066472427464</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8434929870062321</v>
+        <v>0.8281567508788462</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6056,22 +6056,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1103699343020529</v>
+        <v>0.1113799343020529</v>
       </c>
       <c r="C57">
-        <v>9.960092175888349</v>
+        <v>-71.86452154650715</v>
       </c>
       <c r="D57">
-        <v>2406.990092175889</v>
+        <v>2374.651478453493</v>
       </c>
       <c r="E57">
-        <v>2705.630000000001</v>
+        <v>2755.116</v>
       </c>
       <c r="F57">
-        <v>2721.73</v>
+        <v>2771.216</v>
       </c>
       <c r="G57">
         <v>324.7</v>
@@ -6092,37 +6092,37 @@
         <v>330.89</v>
       </c>
       <c r="M57">
-        <v>399.5499640000001</v>
+        <v>406.8145088000001</v>
       </c>
       <c r="N57">
-        <v>-68.65996400000006</v>
+        <v>-75.92450880000007</v>
       </c>
       <c r="O57">
-        <v>-17.16499100000001</v>
+        <v>-18.98112720000002</v>
       </c>
       <c r="P57">
-        <v>-51.49497300000004</v>
+        <v>-56.94338160000005</v>
       </c>
       <c r="Q57">
-        <v>-44.28497300000004</v>
+        <v>-49.73338160000005</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1029917295967609</v>
+        <v>0.104291541633051</v>
       </c>
       <c r="T57">
-        <v>1.114773260751189</v>
+        <v>1.140109016677353</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.2070391877197116</v>
+        <v>0.2033420593675738</v>
       </c>
       <c r="W57">
-        <v>0.1164066472427464</v>
+        <v>0.1169493856848402</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8281567508788462</v>
+        <v>0.8133682374702953</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6138,22 +6138,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1113799343020529</v>
+        <v>0.1440593286430719</v>
       </c>
       <c r="C58">
-        <v>-71.86452154650715</v>
+        <v>-840.8582230626389</v>
       </c>
       <c r="D58">
-        <v>2374.651478453493</v>
+        <v>1655.143776937362</v>
       </c>
       <c r="E58">
-        <v>2755.116</v>
+        <v>2804.602000000001</v>
       </c>
       <c r="F58">
-        <v>2771.216</v>
+        <v>2820.702000000001</v>
       </c>
       <c r="G58">
         <v>324.7</v>
@@ -6174,45 +6174,45 @@
         <v>330.89</v>
       </c>
       <c r="M58">
-        <v>406.8145088000001</v>
+        <v>566.3969616000002</v>
       </c>
       <c r="N58">
-        <v>-75.92450880000007</v>
+        <v>-235.5069616000001</v>
       </c>
       <c r="O58">
-        <v>-18.98112720000002</v>
+        <v>-58.87674040000003</v>
       </c>
       <c r="P58">
-        <v>-56.94338160000005</v>
+        <v>-176.6302212000001</v>
       </c>
       <c r="Q58">
-        <v>-49.73338160000005</v>
+        <v>-169.4202212000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.104291541633051</v>
+        <v>0.1077201689757242</v>
       </c>
       <c r="T58">
-        <v>1.140109016677353</v>
+        <v>1.206939345286771</v>
       </c>
       <c r="U58">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.2033420593675738</v>
+        <v>0.1460503950556503</v>
       </c>
       <c r="W58">
-        <v>0.1169493856848402</v>
+        <v>0.1714730806728254</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y58">
-        <v>0.8133682374702953</v>
+        <v>0.5842015802226012</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6220,22 +6220,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1440593286430719</v>
+        <v>0.1456093286430719</v>
       </c>
       <c r="C59">
-        <v>-840.8582230626389</v>
+        <v>-913.79364167978</v>
       </c>
       <c r="D59">
-        <v>1655.143776937362</v>
+        <v>1631.694358320221</v>
       </c>
       <c r="E59">
-        <v>2804.602000000001</v>
+        <v>2854.088000000001</v>
       </c>
       <c r="F59">
-        <v>2820.702000000001</v>
+        <v>2870.188000000001</v>
       </c>
       <c r="G59">
         <v>324.7</v>
@@ -6256,37 +6256,37 @@
         <v>330.89</v>
       </c>
       <c r="M59">
-        <v>566.3969616000002</v>
+        <v>576.3337504000001</v>
       </c>
       <c r="N59">
-        <v>-235.5069616000001</v>
+        <v>-245.4437504000001</v>
       </c>
       <c r="O59">
-        <v>-58.87674040000003</v>
+        <v>-61.36093760000001</v>
       </c>
       <c r="P59">
-        <v>-176.6302212000001</v>
+        <v>-184.0828128000001</v>
       </c>
       <c r="Q59">
-        <v>-169.4202212000001</v>
+        <v>-176.8728128</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1077201689757242</v>
+        <v>0.1091944587132414</v>
       </c>
       <c r="T59">
-        <v>1.206939345286771</v>
+        <v>1.235675996365027</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1460503950556503</v>
+        <v>0.1435322847960701</v>
       </c>
       <c r="W59">
-        <v>0.1714730806728254</v>
+        <v>0.1719787172129491</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5842015802226012</v>
+        <v>0.5741291391842804</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6302,22 +6302,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1456093286430719</v>
+        <v>0.1471593286430719</v>
       </c>
       <c r="C60">
-        <v>-913.7936416797788</v>
+        <v>-986.073898301818</v>
       </c>
       <c r="D60">
-        <v>1631.694358320221</v>
+        <v>1608.900101698182</v>
       </c>
       <c r="E60">
-        <v>2854.088</v>
+        <v>2903.574</v>
       </c>
       <c r="F60">
-        <v>2870.188</v>
+        <v>2919.674</v>
       </c>
       <c r="G60">
         <v>324.7</v>
@@ -6338,37 +6338,37 @@
         <v>330.89</v>
       </c>
       <c r="M60">
-        <v>576.3337504</v>
+        <v>586.2705392</v>
       </c>
       <c r="N60">
-        <v>-245.4437503999999</v>
+        <v>-255.3805392</v>
       </c>
       <c r="O60">
-        <v>-61.36093759999999</v>
+        <v>-63.8451348</v>
       </c>
       <c r="P60">
-        <v>-184.0828127999999</v>
+        <v>-191.5354044</v>
       </c>
       <c r="Q60">
-        <v>-176.8728127999999</v>
+        <v>-184.3254044</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1091944587132414</v>
+        <v>0.1107406650233204</v>
       </c>
       <c r="T60">
-        <v>1.235675996365027</v>
+        <v>1.265814435300759</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1435322847960702</v>
+        <v>0.1410995342063062</v>
       </c>
       <c r="W60">
-        <v>0.1719787172129491</v>
+        <v>0.1724672135313737</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6376,7 +6376,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5741291391842807</v>
+        <v>0.564398136825225</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6384,22 +6384,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1471593286430719</v>
+        <v>0.1487093286430719</v>
       </c>
       <c r="C61">
-        <v>-986.073898301818</v>
+        <v>-1057.726071865131</v>
       </c>
       <c r="D61">
-        <v>1608.900101698182</v>
+        <v>1586.73392813487</v>
       </c>
       <c r="E61">
-        <v>2903.574</v>
+        <v>2953.06</v>
       </c>
       <c r="F61">
-        <v>2919.674</v>
+        <v>2969.16</v>
       </c>
       <c r="G61">
         <v>324.7</v>
@@ -6420,37 +6420,37 @@
         <v>330.89</v>
       </c>
       <c r="M61">
-        <v>586.2705392</v>
+        <v>596.2073280000001</v>
       </c>
       <c r="N61">
-        <v>-255.3805392</v>
+        <v>-265.317328</v>
       </c>
       <c r="O61">
-        <v>-63.8451348</v>
+        <v>-66.32933200000001</v>
       </c>
       <c r="P61">
-        <v>-191.5354044</v>
+        <v>-198.987996</v>
       </c>
       <c r="Q61">
-        <v>-184.3254044</v>
+        <v>-191.777996</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1107406650233204</v>
+        <v>0.1123641816489035</v>
       </c>
       <c r="T61">
-        <v>1.265814435300759</v>
+        <v>1.297459796183278</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1410995342063062</v>
+        <v>0.1387478753028678</v>
       </c>
       <c r="W61">
-        <v>0.1724672135313737</v>
+        <v>0.1729394266391842</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.564398136825225</v>
+        <v>0.5549915012114712</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6466,22 +6466,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1487093286430719</v>
+        <v>0.1502593286430719</v>
       </c>
       <c r="C62">
-        <v>-1057.726071865131</v>
+        <v>-1128.775769296244</v>
       </c>
       <c r="D62">
-        <v>1586.73392813487</v>
+        <v>1565.170230703756</v>
       </c>
       <c r="E62">
-        <v>2953.06</v>
+        <v>3002.546</v>
       </c>
       <c r="F62">
-        <v>2969.16</v>
+        <v>3018.646</v>
       </c>
       <c r="G62">
         <v>324.7</v>
@@ -6502,37 +6502,37 @@
         <v>330.89</v>
       </c>
       <c r="M62">
-        <v>596.2073280000001</v>
+        <v>606.1441168</v>
       </c>
       <c r="N62">
-        <v>-265.317328</v>
+        <v>-275.2541168</v>
       </c>
       <c r="O62">
-        <v>-66.32933200000001</v>
+        <v>-68.81352919999999</v>
       </c>
       <c r="P62">
-        <v>-198.987996</v>
+        <v>-206.4405876</v>
       </c>
       <c r="Q62">
-        <v>-191.777996</v>
+        <v>-199.2305876</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1123641816489035</v>
+        <v>0.1140709555373369</v>
       </c>
       <c r="T62">
-        <v>1.297459796183278</v>
+        <v>1.330727996085414</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1387478753028678</v>
+        <v>0.1364733199700339</v>
       </c>
       <c r="W62">
-        <v>0.1729394266391842</v>
+        <v>0.1733961573500172</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6540,7 +6540,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5549915012114712</v>
+        <v>0.5458932798801357</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6548,22 +6548,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1502593286430719</v>
+        <v>0.1518093286430719</v>
       </c>
       <c r="C63">
-        <v>-1128.775769296244</v>
+        <v>-1199.247224193751</v>
       </c>
       <c r="D63">
-        <v>1565.170230703756</v>
+        <v>1544.184775806249</v>
       </c>
       <c r="E63">
-        <v>3002.546</v>
+        <v>3052.032</v>
       </c>
       <c r="F63">
-        <v>3018.646</v>
+        <v>3068.132</v>
       </c>
       <c r="G63">
         <v>324.7</v>
@@ -6584,37 +6584,37 @@
         <v>330.89</v>
       </c>
       <c r="M63">
-        <v>606.1441168</v>
+        <v>616.0809056000001</v>
       </c>
       <c r="N63">
-        <v>-275.2541168</v>
+        <v>-285.1909056</v>
       </c>
       <c r="O63">
-        <v>-68.81352919999999</v>
+        <v>-71.2977264</v>
       </c>
       <c r="P63">
-        <v>-206.4405876</v>
+        <v>-213.8931792</v>
       </c>
       <c r="Q63">
-        <v>-199.2305876</v>
+        <v>-206.6831792</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1140709555373369</v>
+        <v>0.1158675596304247</v>
       </c>
       <c r="T63">
-        <v>1.330727996085414</v>
+        <v>1.365747153877135</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.1364733199700339</v>
+        <v>0.1342721373898721</v>
       </c>
       <c r="W63">
-        <v>0.1733961573500172</v>
+        <v>0.1738381548121137</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5458932798801357</v>
+        <v>0.5370885495594883</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6630,22 +6630,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1518093286430719</v>
+        <v>0.1533593286430719</v>
       </c>
       <c r="C64">
-        <v>-1199.247224193751</v>
+        <v>-1269.16338767661</v>
       </c>
       <c r="D64">
-        <v>1544.184775806249</v>
+        <v>1523.754612323391</v>
       </c>
       <c r="E64">
-        <v>3052.032</v>
+        <v>3101.518</v>
       </c>
       <c r="F64">
-        <v>3068.132</v>
+        <v>3117.618</v>
       </c>
       <c r="G64">
         <v>324.7</v>
@@ -6666,37 +6666,37 @@
         <v>330.89</v>
       </c>
       <c r="M64">
-        <v>616.0809056000001</v>
+        <v>626.0176944000001</v>
       </c>
       <c r="N64">
-        <v>-285.1909056</v>
+        <v>-295.1276944000001</v>
       </c>
       <c r="O64">
-        <v>-71.2977264</v>
+        <v>-73.78192360000001</v>
       </c>
       <c r="P64">
-        <v>-213.8931792</v>
+        <v>-221.3457708</v>
       </c>
       <c r="Q64">
-        <v>-206.6831792</v>
+        <v>-214.1357708</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1158675596304247</v>
+        <v>0.117761277458274</v>
       </c>
       <c r="T64">
-        <v>1.365747153877135</v>
+        <v>1.402659239117058</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.1342721373898721</v>
+        <v>0.1321408336217789</v>
       </c>
       <c r="W64">
-        <v>0.1738381548121137</v>
+        <v>0.1742661206087468</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5370885495594883</v>
+        <v>0.5285633344871155</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6712,22 +6712,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1533593286430719</v>
+        <v>0.1549093286430719</v>
       </c>
       <c r="C65">
-        <v>-1269.16338767661</v>
+        <v>-1338.54601211487</v>
       </c>
       <c r="D65">
-        <v>1523.754612323391</v>
+        <v>1503.857987885131</v>
       </c>
       <c r="E65">
-        <v>3101.518</v>
+        <v>3151.004</v>
       </c>
       <c r="F65">
-        <v>3117.618</v>
+        <v>3167.104</v>
       </c>
       <c r="G65">
         <v>324.7</v>
@@ -6748,37 +6748,37 @@
         <v>330.89</v>
       </c>
       <c r="M65">
-        <v>626.0176944000001</v>
+        <v>635.9544832</v>
       </c>
       <c r="N65">
-        <v>-295.1276944000001</v>
+        <v>-305.0644832</v>
       </c>
       <c r="O65">
-        <v>-73.78192360000001</v>
+        <v>-76.2661208</v>
       </c>
       <c r="P65">
-        <v>-221.3457708</v>
+        <v>-228.7983624</v>
       </c>
       <c r="Q65">
-        <v>-214.1357708</v>
+        <v>-221.5883624</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.117761277458274</v>
+        <v>0.119760201832115</v>
       </c>
       <c r="T65">
-        <v>1.402659239117058</v>
+        <v>1.441621995759198</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.1321408336217789</v>
+        <v>0.1300761330964386</v>
       </c>
       <c r="W65">
-        <v>0.1742661206087468</v>
+        <v>0.1746807124742351</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5285633344871155</v>
+        <v>0.5203045323857542</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6794,22 +6794,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1549093286430719</v>
+        <v>0.1564593286430719</v>
       </c>
       <c r="C66">
-        <v>-1338.54601211487</v>
+        <v>-1407.415728385003</v>
       </c>
       <c r="D66">
-        <v>1503.857987885131</v>
+        <v>1484.474271614997</v>
       </c>
       <c r="E66">
-        <v>3151.004</v>
+        <v>3200.49</v>
       </c>
       <c r="F66">
-        <v>3167.104</v>
+        <v>3216.59</v>
       </c>
       <c r="G66">
         <v>324.7</v>
@@ -6830,37 +6830,37 @@
         <v>330.89</v>
       </c>
       <c r="M66">
-        <v>635.9544832</v>
+        <v>645.8912720000001</v>
       </c>
       <c r="N66">
-        <v>-305.0644832</v>
+        <v>-315.001272</v>
       </c>
       <c r="O66">
-        <v>-76.2661208</v>
+        <v>-78.75031800000001</v>
       </c>
       <c r="P66">
-        <v>-228.7983624</v>
+        <v>-236.250954</v>
       </c>
       <c r="Q66">
-        <v>-221.5883624</v>
+        <v>-229.040954</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.119760201832115</v>
+        <v>0.1218733504558897</v>
       </c>
       <c r="T66">
-        <v>1.441621995759198</v>
+        <v>1.482811195638033</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.1300761330964386</v>
+        <v>0.1280749618180318</v>
       </c>
       <c r="W66">
-        <v>0.1746807124742351</v>
+        <v>0.1750825476669392</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6868,7 +6868,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5203045323857542</v>
+        <v>0.5122998472721272</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6876,22 +6876,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1564593286430719</v>
+        <v>0.1580093286430719</v>
       </c>
       <c r="C67">
-        <v>-1407.415728385003</v>
+        <v>-1475.792117226644</v>
       </c>
       <c r="D67">
-        <v>1484.474271614997</v>
+        <v>1465.583882773356</v>
       </c>
       <c r="E67">
-        <v>3200.49</v>
+        <v>3249.976000000001</v>
       </c>
       <c r="F67">
-        <v>3216.59</v>
+        <v>3266.076</v>
       </c>
       <c r="G67">
         <v>324.7</v>
@@ -6912,37 +6912,37 @@
         <v>330.89</v>
       </c>
       <c r="M67">
-        <v>645.8912720000001</v>
+        <v>655.8280608000001</v>
       </c>
       <c r="N67">
-        <v>-315.001272</v>
+        <v>-324.9380608000001</v>
       </c>
       <c r="O67">
-        <v>-78.75031800000001</v>
+        <v>-81.23451520000002</v>
       </c>
       <c r="P67">
-        <v>-236.250954</v>
+        <v>-243.7035456</v>
       </c>
       <c r="Q67">
-        <v>-229.040954</v>
+        <v>-236.4935456</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1218733504558897</v>
+        <v>0.1241108019398864</v>
       </c>
       <c r="T67">
-        <v>1.482811195638033</v>
+        <v>1.526423289627386</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.1280749618180318</v>
+        <v>0.1261344320935162</v>
       </c>
       <c r="W67">
-        <v>0.1750825476669392</v>
+        <v>0.175472206035622</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6950,7 +6950,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.5122998472721272</v>
+        <v>0.5045377283740646</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6958,22 +6958,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1580093286430719</v>
+        <v>0.1833682100023654</v>
       </c>
       <c r="C68">
-        <v>-1475.792117226644</v>
+        <v>-1777.824351151211</v>
       </c>
       <c r="D68">
-        <v>1465.583882773356</v>
+        <v>1213.037648848789</v>
       </c>
       <c r="E68">
-        <v>3249.976000000001</v>
+        <v>3299.462</v>
       </c>
       <c r="F68">
-        <v>3266.076</v>
+        <v>3315.562</v>
       </c>
       <c r="G68">
         <v>324.7</v>
@@ -6994,45 +6994,45 @@
         <v>330.89</v>
       </c>
       <c r="M68">
-        <v>655.8280608000001</v>
+        <v>781.8095196000002</v>
       </c>
       <c r="N68">
-        <v>-324.9380608000001</v>
+        <v>-450.9195196000001</v>
       </c>
       <c r="O68">
-        <v>-81.23451520000002</v>
+        <v>-112.7298799</v>
       </c>
       <c r="P68">
-        <v>-243.7035456</v>
+        <v>-338.1896397000001</v>
       </c>
       <c r="Q68">
-        <v>-236.4935456</v>
+        <v>-330.9796397000001</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1241108019398864</v>
+        <v>0.1275713758147117</v>
       </c>
       <c r="T68">
-        <v>1.526423289627386</v>
+        <v>1.593876315610496</v>
       </c>
       <c r="U68">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1261344320935162</v>
+        <v>0.1058090211568716</v>
       </c>
       <c r="W68">
-        <v>0.175472206035622</v>
+        <v>0.2108502328112097</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y68">
-        <v>0.5045377283740646</v>
+        <v>0.4232360846274863</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7040,22 +7040,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1833682100023654</v>
+        <v>0.1852682100023654</v>
       </c>
       <c r="C69">
-        <v>-1777.824351151211</v>
+        <v>-1842.772035269669</v>
       </c>
       <c r="D69">
-        <v>1213.037648848789</v>
+        <v>1197.575964730331</v>
       </c>
       <c r="E69">
-        <v>3299.462</v>
+        <v>3348.948000000001</v>
       </c>
       <c r="F69">
-        <v>3315.562</v>
+        <v>3365.048000000001</v>
       </c>
       <c r="G69">
         <v>324.7</v>
@@ -7076,37 +7076,37 @@
         <v>330.89</v>
       </c>
       <c r="M69">
-        <v>781.8095196000002</v>
+        <v>793.4783184000001</v>
       </c>
       <c r="N69">
-        <v>-450.9195196000001</v>
+        <v>-462.5883184000001</v>
       </c>
       <c r="O69">
-        <v>-112.7298799</v>
+        <v>-115.6470796</v>
       </c>
       <c r="P69">
-        <v>-338.1896397000001</v>
+        <v>-346.9412388000001</v>
       </c>
       <c r="Q69">
-        <v>-330.9796397000001</v>
+        <v>-339.7312388000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1275713758147117</v>
+        <v>0.1301267313089214</v>
       </c>
       <c r="T69">
-        <v>1.593876315610496</v>
+        <v>1.643684950473324</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1058090211568716</v>
+        <v>0.1042530061398587</v>
       </c>
       <c r="W69">
-        <v>0.2108502328112097</v>
+        <v>0.2112171411522213</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.4232360846274863</v>
+        <v>0.417012024559435</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7122,22 +7122,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1852682100023654</v>
+        <v>0.1871682100023654</v>
       </c>
       <c r="C70">
-        <v>-1842.772035269669</v>
+        <v>-1907.330523123443</v>
       </c>
       <c r="D70">
-        <v>1197.575964730331</v>
+        <v>1182.503476876557</v>
       </c>
       <c r="E70">
-        <v>3348.948000000001</v>
+        <v>3398.434000000001</v>
       </c>
       <c r="F70">
-        <v>3365.048000000001</v>
+        <v>3414.534000000001</v>
       </c>
       <c r="G70">
         <v>324.7</v>
@@ -7158,37 +7158,37 @@
         <v>330.89</v>
       </c>
       <c r="M70">
-        <v>793.4783184000001</v>
+        <v>805.1471172000001</v>
       </c>
       <c r="N70">
-        <v>-462.5883184000001</v>
+        <v>-474.2571172000001</v>
       </c>
       <c r="O70">
-        <v>-115.6470796</v>
+        <v>-118.5642793</v>
       </c>
       <c r="P70">
-        <v>-346.9412388000001</v>
+        <v>-355.6928379000001</v>
       </c>
       <c r="Q70">
-        <v>-339.7312388000001</v>
+        <v>-348.4828379000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1301267313089214</v>
+        <v>0.1328469484479189</v>
       </c>
       <c r="T70">
-        <v>1.643684950473324</v>
+        <v>1.696707045649883</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1042530061398587</v>
+        <v>0.102742093007397</v>
       </c>
       <c r="W70">
-        <v>0.2112171411522213</v>
+        <v>0.2115734144688558</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.417012024559435</v>
+        <v>0.4109683720295881</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7204,22 +7204,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1871682100023654</v>
+        <v>0.1890682100023653</v>
       </c>
       <c r="C71">
-        <v>-1907.330523123443</v>
+        <v>-1971.514327136045</v>
       </c>
       <c r="D71">
-        <v>1182.503476876557</v>
+        <v>1167.805672863955</v>
       </c>
       <c r="E71">
-        <v>3398.434000000001</v>
+        <v>3447.920000000001</v>
       </c>
       <c r="F71">
-        <v>3414.534000000001</v>
+        <v>3464.02</v>
       </c>
       <c r="G71">
         <v>324.7</v>
@@ -7240,37 +7240,37 @@
         <v>330.89</v>
       </c>
       <c r="M71">
-        <v>805.1471172000001</v>
+        <v>816.8159160000001</v>
       </c>
       <c r="N71">
-        <v>-474.2571172000001</v>
+        <v>-485.9259160000001</v>
       </c>
       <c r="O71">
-        <v>-118.5642793</v>
+        <v>-121.481479</v>
       </c>
       <c r="P71">
-        <v>-355.6928379000001</v>
+        <v>-364.4444370000001</v>
       </c>
       <c r="Q71">
-        <v>-348.4828379000001</v>
+        <v>-357.2344370000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1328469484479189</v>
+        <v>0.1357485133961829</v>
       </c>
       <c r="T71">
-        <v>1.696707045649883</v>
+        <v>1.753263947171546</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.102742093007397</v>
+        <v>0.1012743488215771</v>
       </c>
       <c r="W71">
-        <v>0.2115734144688558</v>
+        <v>0.2119195085478721</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.4109683720295881</v>
+        <v>0.4050973952863083</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7286,22 +7286,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1890682100023653</v>
+        <v>0.1909682100023654</v>
       </c>
       <c r="C72">
-        <v>-1971.514327136045</v>
+        <v>-2035.337247066345</v>
       </c>
       <c r="D72">
-        <v>1167.805672863955</v>
+        <v>1153.468752933656</v>
       </c>
       <c r="E72">
-        <v>3447.920000000001</v>
+        <v>3497.406000000001</v>
       </c>
       <c r="F72">
-        <v>3464.02</v>
+        <v>3513.506000000001</v>
       </c>
       <c r="G72">
         <v>324.7</v>
@@ -7322,37 +7322,37 @@
         <v>330.89</v>
       </c>
       <c r="M72">
-        <v>816.8159160000001</v>
+        <v>828.4847148000002</v>
       </c>
       <c r="N72">
-        <v>-485.9259160000001</v>
+        <v>-497.5947148000002</v>
       </c>
       <c r="O72">
-        <v>-121.481479</v>
+        <v>-124.3986787</v>
       </c>
       <c r="P72">
-        <v>-364.4444370000001</v>
+        <v>-373.1960361000001</v>
       </c>
       <c r="Q72">
-        <v>-357.2344370000001</v>
+        <v>-365.9860361000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1357485133961829</v>
+        <v>0.1388501862719133</v>
       </c>
       <c r="T72">
-        <v>1.753263947171546</v>
+        <v>1.81372132466022</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1012743488215771</v>
+        <v>0.09984794954239992</v>
       </c>
       <c r="W72">
-        <v>0.2119195085478721</v>
+        <v>0.2122558534979021</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4050973952863083</v>
+        <v>0.3993917981695997</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7368,22 +7368,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1909682100023654</v>
+        <v>0.1928682100023653</v>
       </c>
       <c r="C73">
-        <v>-2035.337247066344</v>
+        <v>-2098.81241322423</v>
       </c>
       <c r="D73">
-        <v>1153.468752933656</v>
+        <v>1139.47958677577</v>
       </c>
       <c r="E73">
-        <v>3497.406</v>
+        <v>3546.892</v>
       </c>
       <c r="F73">
-        <v>3513.506</v>
+        <v>3562.992</v>
       </c>
       <c r="G73">
         <v>324.7</v>
@@ -7404,37 +7404,37 @@
         <v>330.89</v>
       </c>
       <c r="M73">
-        <v>828.4847148</v>
+        <v>840.1535136000001</v>
       </c>
       <c r="N73">
-        <v>-497.5947148</v>
+        <v>-509.2635136000001</v>
       </c>
       <c r="O73">
-        <v>-124.3986787</v>
+        <v>-127.3158784</v>
       </c>
       <c r="P73">
-        <v>-373.1960361</v>
+        <v>-381.9476352</v>
       </c>
       <c r="Q73">
-        <v>-365.9860361</v>
+        <v>-374.7376352000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1388501862719133</v>
+        <v>0.1421734072101959</v>
       </c>
       <c r="T73">
-        <v>1.81372132466022</v>
+        <v>1.878497086255227</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.09984794954239995</v>
+        <v>0.09846117246542216</v>
       </c>
       <c r="W73">
-        <v>0.2122558534979021</v>
+        <v>0.2125828555326535</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7442,7 +7442,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3993917981695998</v>
+        <v>0.3938446898616886</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7450,22 +7450,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1928682100023653</v>
+        <v>0.1947682100023653</v>
       </c>
       <c r="C74">
-        <v>-2098.81241322423</v>
+        <v>-2161.952326579264</v>
       </c>
       <c r="D74">
-        <v>1139.47958677577</v>
+        <v>1125.825673420736</v>
       </c>
       <c r="E74">
-        <v>3546.892</v>
+        <v>3596.378</v>
       </c>
       <c r="F74">
-        <v>3562.992</v>
+        <v>3612.478</v>
       </c>
       <c r="G74">
         <v>324.7</v>
@@ -7486,37 +7486,37 @@
         <v>330.89</v>
       </c>
       <c r="M74">
-        <v>840.1535136000001</v>
+        <v>851.8223124000001</v>
       </c>
       <c r="N74">
-        <v>-509.2635136000001</v>
+        <v>-520.9323124</v>
       </c>
       <c r="O74">
-        <v>-127.3158784</v>
+        <v>-130.2330781</v>
       </c>
       <c r="P74">
-        <v>-381.9476352</v>
+        <v>-390.6992343</v>
       </c>
       <c r="Q74">
-        <v>-374.7376352000001</v>
+        <v>-383.4892343</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1421734072101959</v>
+        <v>0.1457427926624254</v>
       </c>
       <c r="T74">
-        <v>1.878497086255227</v>
+        <v>1.948071052412828</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.09846117246542216</v>
+        <v>0.09711238928096431</v>
       </c>
       <c r="W74">
-        <v>0.2125828555326535</v>
+        <v>0.2129008986075486</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7524,7 +7524,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3938446898616886</v>
+        <v>0.3884495571238573</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7532,22 +7532,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1947682100023653</v>
+        <v>0.1966682100023654</v>
       </c>
       <c r="C75">
-        <v>-2161.952326579264</v>
+        <v>-2224.768896019851</v>
       </c>
       <c r="D75">
-        <v>1125.825673420736</v>
+        <v>1112.495103980149</v>
       </c>
       <c r="E75">
-        <v>3596.378</v>
+        <v>3645.864</v>
       </c>
       <c r="F75">
-        <v>3612.478</v>
+        <v>3661.964</v>
       </c>
       <c r="G75">
         <v>324.7</v>
@@ -7568,37 +7568,37 @@
         <v>330.89</v>
       </c>
       <c r="M75">
-        <v>851.8223124000001</v>
+        <v>863.4911112000001</v>
       </c>
       <c r="N75">
-        <v>-520.9323124</v>
+        <v>-532.6011112000001</v>
       </c>
       <c r="O75">
-        <v>-130.2330781</v>
+        <v>-133.1502778</v>
       </c>
       <c r="P75">
-        <v>-390.6992343</v>
+        <v>-399.4508334000001</v>
       </c>
       <c r="Q75">
-        <v>-383.4892343</v>
+        <v>-392.2408334000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1457427926624254</v>
+        <v>0.1495867462263648</v>
       </c>
       <c r="T75">
-        <v>1.948071052412828</v>
+        <v>2.022996862121014</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.09711238928096431</v>
+        <v>0.09580005969608643</v>
       </c>
       <c r="W75">
-        <v>0.2129008986075486</v>
+        <v>0.2132103459236628</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3884495571238573</v>
+        <v>0.3832002387843456</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7614,22 +7614,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1966682100023654</v>
+        <v>0.1985682100023653</v>
       </c>
       <c r="C76">
-        <v>-2224.768896019851</v>
+        <v>-2287.273472996324</v>
       </c>
       <c r="D76">
-        <v>1112.495103980149</v>
+        <v>1099.476527003677</v>
       </c>
       <c r="E76">
-        <v>3645.864</v>
+        <v>3695.35</v>
       </c>
       <c r="F76">
-        <v>3661.964</v>
+        <v>3711.45</v>
       </c>
       <c r="G76">
         <v>324.7</v>
@@ -7650,37 +7650,37 @@
         <v>330.89</v>
       </c>
       <c r="M76">
-        <v>863.4911112000001</v>
+        <v>875.1599100000001</v>
       </c>
       <c r="N76">
-        <v>-532.6011112000001</v>
+        <v>-544.26991</v>
       </c>
       <c r="O76">
-        <v>-133.1502778</v>
+        <v>-136.0674775</v>
       </c>
       <c r="P76">
-        <v>-399.4508334000001</v>
+        <v>-408.2024325</v>
       </c>
       <c r="Q76">
-        <v>-392.2408334000001</v>
+        <v>-400.9924325</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1495867462263648</v>
+        <v>0.1537382160754194</v>
       </c>
       <c r="T76">
-        <v>2.022996862121014</v>
+        <v>2.103916736605855</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.09580005969608643</v>
+        <v>0.09452272556680527</v>
       </c>
       <c r="W76">
-        <v>0.2132103459236628</v>
+        <v>0.2135115413113473</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7688,7 +7688,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3832002387843456</v>
+        <v>0.3780909022672212</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7696,22 +7696,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1985682100023653</v>
+        <v>0.2004682100023654</v>
       </c>
       <c r="C77">
-        <v>-2287.273472996324</v>
+        <v>-2349.476883759787</v>
       </c>
       <c r="D77">
-        <v>1099.476527003677</v>
+        <v>1086.759116240213</v>
       </c>
       <c r="E77">
-        <v>3695.35</v>
+        <v>3744.836</v>
       </c>
       <c r="F77">
-        <v>3711.45</v>
+        <v>3760.936</v>
       </c>
       <c r="G77">
         <v>324.7</v>
@@ -7732,37 +7732,37 @@
         <v>330.89</v>
       </c>
       <c r="M77">
-        <v>875.1599100000001</v>
+        <v>886.8287088000001</v>
       </c>
       <c r="N77">
-        <v>-544.26991</v>
+        <v>-555.9387088000001</v>
       </c>
       <c r="O77">
-        <v>-136.0674775</v>
+        <v>-138.9846772</v>
       </c>
       <c r="P77">
-        <v>-408.2024325</v>
+        <v>-416.9540316000001</v>
       </c>
       <c r="Q77">
-        <v>-400.9924325</v>
+        <v>-409.7440316000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1537382160754194</v>
+        <v>0.1582356417452286</v>
       </c>
       <c r="T77">
-        <v>2.103916736605855</v>
+        <v>2.191579933964432</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.09452272556680527</v>
+        <v>0.09327900549355783</v>
       </c>
       <c r="W77">
-        <v>0.2135115413113473</v>
+        <v>0.2138048105046191</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7770,7 +7770,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3780909022672212</v>
+        <v>0.3731160219742313</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7778,22 +7778,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2004682100023654</v>
+        <v>0.2023682100023653</v>
       </c>
       <c r="C78">
-        <v>-2349.476883759787</v>
+        <v>-2411.389459389134</v>
       </c>
       <c r="D78">
-        <v>1086.759116240213</v>
+        <v>1074.332540610867</v>
       </c>
       <c r="E78">
-        <v>3744.836</v>
+        <v>3794.322000000001</v>
       </c>
       <c r="F78">
-        <v>3760.936</v>
+        <v>3810.422</v>
       </c>
       <c r="G78">
         <v>324.7</v>
@@ -7814,37 +7814,37 @@
         <v>330.89</v>
       </c>
       <c r="M78">
-        <v>886.8287088000001</v>
+        <v>898.4975076000002</v>
       </c>
       <c r="N78">
-        <v>-555.9387088000001</v>
+        <v>-567.6075076000002</v>
       </c>
       <c r="O78">
-        <v>-138.9846772</v>
+        <v>-141.9018769</v>
       </c>
       <c r="P78">
-        <v>-416.9540316000001</v>
+        <v>-425.7056307000001</v>
       </c>
       <c r="Q78">
-        <v>-409.7440316000001</v>
+        <v>-418.4956307000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1582356417452286</v>
+        <v>0.1631241479080646</v>
       </c>
       <c r="T78">
-        <v>2.191579933964432</v>
+        <v>2.286866018049842</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.09327900549355783</v>
+        <v>0.09206758983779734</v>
       </c>
       <c r="W78">
-        <v>0.2138048105046191</v>
+        <v>0.2140904623162474</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3731160219742313</v>
+        <v>0.3682703593511892</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7860,22 +7860,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2023682100023653</v>
+        <v>0.2042682100023654</v>
       </c>
       <c r="C79">
-        <v>-2411.389459389134</v>
+        <v>-2473.021063781292</v>
       </c>
       <c r="D79">
-        <v>1074.332540610867</v>
+        <v>1062.186936218708</v>
       </c>
       <c r="E79">
-        <v>3794.322000000001</v>
+        <v>3843.808</v>
       </c>
       <c r="F79">
-        <v>3810.422</v>
+        <v>3859.908</v>
       </c>
       <c r="G79">
         <v>324.7</v>
@@ -7896,37 +7896,37 @@
         <v>330.89</v>
       </c>
       <c r="M79">
-        <v>898.4975076000002</v>
+        <v>910.1663064000002</v>
       </c>
       <c r="N79">
-        <v>-567.6075076000002</v>
+        <v>-579.2763064000001</v>
       </c>
       <c r="O79">
-        <v>-141.9018769</v>
+        <v>-144.8190766</v>
       </c>
       <c r="P79">
-        <v>-425.7056307000001</v>
+        <v>-434.4572298000001</v>
       </c>
       <c r="Q79">
-        <v>-418.4956307000002</v>
+        <v>-427.2472298000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1631241479080646</v>
+        <v>0.1684570637220675</v>
       </c>
       <c r="T79">
-        <v>2.286866018049842</v>
+        <v>2.390814473415745</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.09206758983779734</v>
+        <v>0.09088723612192814</v>
       </c>
       <c r="W79">
-        <v>0.2140904623162474</v>
+        <v>0.2143687897224494</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3682703593511892</v>
+        <v>0.3635489444877126</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7942,22 +7942,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2042682100023654</v>
+        <v>0.2061682100023653</v>
       </c>
       <c r="C80">
-        <v>-2473.021063781292</v>
+        <v>-2534.381119764073</v>
       </c>
       <c r="D80">
-        <v>1062.186936218708</v>
+        <v>1050.312880235928</v>
       </c>
       <c r="E80">
-        <v>3843.808</v>
+        <v>3893.294000000001</v>
       </c>
       <c r="F80">
-        <v>3859.908</v>
+        <v>3909.394000000001</v>
       </c>
       <c r="G80">
         <v>324.7</v>
@@ -7978,37 +7978,37 @@
         <v>330.89</v>
       </c>
       <c r="M80">
-        <v>910.1663064000002</v>
+        <v>921.8351052000002</v>
       </c>
       <c r="N80">
-        <v>-579.2763064000001</v>
+        <v>-590.9451052000002</v>
       </c>
       <c r="O80">
-        <v>-144.8190766</v>
+        <v>-147.7362763</v>
       </c>
       <c r="P80">
-        <v>-434.4572298000001</v>
+        <v>-443.2088289000001</v>
       </c>
       <c r="Q80">
-        <v>-427.2472298000001</v>
+        <v>-435.9988289000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1684570637220675</v>
+        <v>0.1742978762802612</v>
       </c>
       <c r="T80">
-        <v>2.390814473415745</v>
+        <v>2.504662781673637</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.09088723612192814</v>
+        <v>0.0897367647786126</v>
       </c>
       <c r="W80">
-        <v>0.2143687897224494</v>
+        <v>0.2146400708652031</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3635489444877126</v>
+        <v>0.3589470591144504</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8024,22 +8024,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2061682100023653</v>
+        <v>0.2080682100023654</v>
       </c>
       <c r="C81">
-        <v>-2534.381119764073</v>
+        <v>-2595.478633476895</v>
       </c>
       <c r="D81">
-        <v>1050.312880235928</v>
+        <v>1038.701366523106</v>
       </c>
       <c r="E81">
-        <v>3893.294000000001</v>
+        <v>3942.780000000001</v>
       </c>
       <c r="F81">
-        <v>3909.394000000001</v>
+        <v>3958.880000000001</v>
       </c>
       <c r="G81">
         <v>324.7</v>
@@ -8060,37 +8060,37 @@
         <v>330.89</v>
       </c>
       <c r="M81">
-        <v>921.8351052000002</v>
+        <v>933.5039040000001</v>
       </c>
       <c r="N81">
-        <v>-590.9451052000002</v>
+        <v>-602.613904</v>
       </c>
       <c r="O81">
-        <v>-147.7362763</v>
+        <v>-150.653476</v>
       </c>
       <c r="P81">
-        <v>-443.2088289000001</v>
+        <v>-451.960428</v>
       </c>
       <c r="Q81">
-        <v>-435.9988289000001</v>
+        <v>-444.7504280000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1742978762802612</v>
+        <v>0.1807227700942743</v>
       </c>
       <c r="T81">
-        <v>2.504662781673637</v>
+        <v>2.629895920757319</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0897367647786126</v>
+        <v>0.08861505521887994</v>
       </c>
       <c r="W81">
-        <v>0.2146400708652031</v>
+        <v>0.2149045699793881</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8098,7 +8098,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3589470591144504</v>
+        <v>0.3544602208755199</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8106,22 +8106,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2080682100023654</v>
+        <v>0.2099682100023653</v>
       </c>
       <c r="C82">
-        <v>-2595.478633476895</v>
+        <v>-2656.322217152002</v>
       </c>
       <c r="D82">
-        <v>1038.701366523106</v>
+        <v>1027.343782847998</v>
       </c>
       <c r="E82">
-        <v>3942.780000000001</v>
+        <v>3992.266000000001</v>
       </c>
       <c r="F82">
-        <v>3958.880000000001</v>
+        <v>4008.366</v>
       </c>
       <c r="G82">
         <v>324.7</v>
@@ -8142,37 +8142,37 @@
         <v>330.89</v>
       </c>
       <c r="M82">
-        <v>933.5039040000001</v>
+        <v>945.1727028000001</v>
       </c>
       <c r="N82">
-        <v>-602.613904</v>
+        <v>-614.2827028000002</v>
       </c>
       <c r="O82">
-        <v>-150.653476</v>
+        <v>-153.5706757</v>
       </c>
       <c r="P82">
-        <v>-451.960428</v>
+        <v>-460.7120271000001</v>
       </c>
       <c r="Q82">
-        <v>-444.7504280000001</v>
+        <v>-453.5020271000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1807227700942743</v>
+        <v>0.1878239685202887</v>
       </c>
       <c r="T82">
-        <v>2.629895920757319</v>
+        <v>2.76831149553402</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.08861505521887994</v>
+        <v>0.08752104219148636</v>
       </c>
       <c r="W82">
-        <v>0.2149045699793881</v>
+        <v>0.2151625382512475</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3544602208755199</v>
+        <v>0.3500841687659454</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8188,22 +8188,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2099682100023653</v>
+        <v>0.2118682100023654</v>
       </c>
       <c r="C83">
-        <v>-2656.322217152002</v>
+        <v>-2716.920110417229</v>
       </c>
       <c r="D83">
-        <v>1027.343782847998</v>
+        <v>1016.231889582772</v>
       </c>
       <c r="E83">
-        <v>3992.266000000001</v>
+        <v>4041.752000000001</v>
       </c>
       <c r="F83">
-        <v>4008.366</v>
+        <v>4057.852000000001</v>
       </c>
       <c r="G83">
         <v>324.7</v>
@@ -8224,37 +8224,37 @@
         <v>330.89</v>
       </c>
       <c r="M83">
-        <v>945.1727028000001</v>
+        <v>956.8415016000002</v>
       </c>
       <c r="N83">
-        <v>-614.2827028000002</v>
+        <v>-625.9515016000003</v>
       </c>
       <c r="O83">
-        <v>-153.5706757</v>
+        <v>-156.4878754000001</v>
       </c>
       <c r="P83">
-        <v>-460.7120271000001</v>
+        <v>-469.4636262000002</v>
       </c>
       <c r="Q83">
-        <v>-453.5020271000001</v>
+        <v>-462.2536262000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1878239685202887</v>
+        <v>0.1957141889936381</v>
       </c>
       <c r="T83">
-        <v>2.76831149553402</v>
+        <v>2.922106578619244</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.08752104219148636</v>
+        <v>0.08645371240866334</v>
       </c>
       <c r="W83">
-        <v>0.2151625382512475</v>
+        <v>0.2154142146140372</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8262,7 +8262,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3500841687659454</v>
+        <v>0.3458148496346534</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8270,22 +8270,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2118682100023654</v>
+        <v>0.2137682100023653</v>
       </c>
       <c r="C84">
-        <v>-2716.920110417229</v>
+        <v>-2777.280200231083</v>
       </c>
       <c r="D84">
-        <v>1016.231889582772</v>
+        <v>1005.357799768918</v>
       </c>
       <c r="E84">
-        <v>4041.752000000001</v>
+        <v>4091.238000000001</v>
       </c>
       <c r="F84">
-        <v>4057.852000000001</v>
+        <v>4107.338000000001</v>
       </c>
       <c r="G84">
         <v>324.7</v>
@@ -8306,37 +8306,37 @@
         <v>330.89</v>
       </c>
       <c r="M84">
-        <v>956.8415016000002</v>
+        <v>968.5103004000002</v>
       </c>
       <c r="N84">
-        <v>-625.9515016000003</v>
+        <v>-637.6203004000001</v>
       </c>
       <c r="O84">
-        <v>-156.4878754000001</v>
+        <v>-159.4050751</v>
       </c>
       <c r="P84">
-        <v>-469.4636262000002</v>
+        <v>-478.2152253000001</v>
       </c>
       <c r="Q84">
-        <v>-462.2536262000002</v>
+        <v>-471.0052253000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.1957141889936381</v>
+        <v>0.2045326706991462</v>
       </c>
       <c r="T84">
-        <v>2.922106578619244</v>
+        <v>3.093995200890964</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.08645371240866334</v>
+        <v>0.08541210141578788</v>
       </c>
       <c r="W84">
-        <v>0.2154142146140372</v>
+        <v>0.2156598264861572</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3458148496346534</v>
+        <v>0.3416484056631516</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8352,22 +8352,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2137682100023653</v>
+        <v>0.2156682100023654</v>
       </c>
       <c r="C85">
-        <v>-2777.280200231083</v>
+        <v>-2837.410039551509</v>
       </c>
       <c r="D85">
-        <v>1005.357799768918</v>
+        <v>994.7139604484919</v>
       </c>
       <c r="E85">
-        <v>4091.238000000001</v>
+        <v>4140.724</v>
       </c>
       <c r="F85">
-        <v>4107.338000000001</v>
+        <v>4156.824000000001</v>
       </c>
       <c r="G85">
         <v>324.7</v>
@@ -8388,37 +8388,37 @@
         <v>330.89</v>
       </c>
       <c r="M85">
-        <v>968.5103004000002</v>
+        <v>980.1790992000001</v>
       </c>
       <c r="N85">
-        <v>-637.6203004000001</v>
+        <v>-649.2890992</v>
       </c>
       <c r="O85">
-        <v>-159.4050751</v>
+        <v>-162.3222748</v>
       </c>
       <c r="P85">
-        <v>-478.2152253000001</v>
+        <v>-486.9668244</v>
       </c>
       <c r="Q85">
-        <v>-471.0052253000001</v>
+        <v>-479.7568244</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2045326706991462</v>
+        <v>0.2144534626178429</v>
       </c>
       <c r="T85">
-        <v>3.093995200890964</v>
+        <v>3.28736990094665</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.08541210141578788</v>
+        <v>0.08439529068464756</v>
       </c>
       <c r="W85">
-        <v>0.2156598264861572</v>
+        <v>0.2158995904565601</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3416484056631516</v>
+        <v>0.3375811627385903</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8434,22 +8434,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2156682100023653</v>
+        <v>0.2175682100023654</v>
       </c>
       <c r="C86">
-        <v>-2837.410039551509</v>
+        <v>-2897.316864831169</v>
       </c>
       <c r="D86">
-        <v>994.7139604484919</v>
+        <v>984.2931351688312</v>
       </c>
       <c r="E86">
-        <v>4140.724</v>
+        <v>4190.21</v>
       </c>
       <c r="F86">
-        <v>4156.824000000001</v>
+        <v>4206.31</v>
       </c>
       <c r="G86">
         <v>324.7</v>
@@ -8470,37 +8470,37 @@
         <v>330.89</v>
       </c>
       <c r="M86">
-        <v>980.1790992000001</v>
+        <v>991.8478980000001</v>
       </c>
       <c r="N86">
-        <v>-649.2890992</v>
+        <v>-660.9578980000001</v>
       </c>
       <c r="O86">
-        <v>-162.3222748</v>
+        <v>-165.2394745</v>
       </c>
       <c r="P86">
-        <v>-486.9668244</v>
+        <v>-495.7184235000001</v>
       </c>
       <c r="Q86">
-        <v>-479.7568244</v>
+        <v>-488.5084235000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2144534626178428</v>
+        <v>0.2256970267923657</v>
       </c>
       <c r="T86">
-        <v>3.287369900946647</v>
+        <v>3.506527894343091</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.08439529068464756</v>
+        <v>0.08340240491188701</v>
       </c>
       <c r="W86">
-        <v>0.2158995904565601</v>
+        <v>0.216133712921777</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3375811627385903</v>
+        <v>0.333609619647548</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8516,22 +8516,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2175682100023654</v>
+        <v>0.2194682100023653</v>
       </c>
       <c r="C87">
-        <v>-2897.316864831169</v>
+        <v>-2957.007612424431</v>
       </c>
       <c r="D87">
-        <v>984.2931351688312</v>
+        <v>974.0883875755694</v>
       </c>
       <c r="E87">
-        <v>4190.21</v>
+        <v>4239.696</v>
       </c>
       <c r="F87">
-        <v>4206.31</v>
+        <v>4255.796</v>
       </c>
       <c r="G87">
         <v>324.7</v>
@@ -8552,37 +8552,37 @@
         <v>330.89</v>
       </c>
       <c r="M87">
-        <v>991.8478980000001</v>
+        <v>1003.5166968</v>
       </c>
       <c r="N87">
-        <v>-660.9578980000001</v>
+        <v>-672.6266968</v>
       </c>
       <c r="O87">
-        <v>-165.2394745</v>
+        <v>-168.1566742</v>
       </c>
       <c r="P87">
-        <v>-495.7184235000001</v>
+        <v>-504.4700226</v>
       </c>
       <c r="Q87">
-        <v>-488.5084235000001</v>
+        <v>-497.2600226</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2256970267923657</v>
+        <v>0.2385468144203918</v>
       </c>
       <c r="T87">
-        <v>3.506527894343091</v>
+        <v>3.756994172510454</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.08340240491188701</v>
+        <v>0.08243260950593484</v>
       </c>
       <c r="W87">
-        <v>0.216133712921777</v>
+        <v>0.2163623906785005</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.333609619647548</v>
+        <v>0.3297304380237394</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8598,22 +8598,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2194682100023653</v>
+        <v>0.2213682100023653</v>
       </c>
       <c r="C88">
-        <v>-2957.007612424431</v>
+        <v>-3016.488933984219</v>
       </c>
       <c r="D88">
-        <v>974.0883875755694</v>
+        <v>964.0930660157809</v>
       </c>
       <c r="E88">
-        <v>4239.696</v>
+        <v>4289.182</v>
       </c>
       <c r="F88">
-        <v>4255.796</v>
+        <v>4305.282</v>
       </c>
       <c r="G88">
         <v>324.7</v>
@@ -8634,37 +8634,37 @@
         <v>330.89</v>
       </c>
       <c r="M88">
-        <v>1003.5166968</v>
+        <v>1015.1854956</v>
       </c>
       <c r="N88">
-        <v>-672.6266968</v>
+        <v>-684.2954956000001</v>
       </c>
       <c r="O88">
-        <v>-168.1566742</v>
+        <v>-171.0738739</v>
       </c>
       <c r="P88">
-        <v>-504.4700226</v>
+        <v>-513.2216217</v>
       </c>
       <c r="Q88">
-        <v>-497.2600226</v>
+        <v>-506.0116217</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2385468144203918</v>
+        <v>0.2533734924527296</v>
       </c>
       <c r="T88">
-        <v>3.756994172510454</v>
+        <v>4.045993724242028</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.08243260950593484</v>
+        <v>0.08148510824724593</v>
       </c>
       <c r="W88">
-        <v>0.2163623906785005</v>
+        <v>0.2165858114752994</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3297304380237394</v>
+        <v>0.3259404329889837</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8680,22 +8680,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2213682100023653</v>
+        <v>0.2232682100023654</v>
       </c>
       <c r="C89">
-        <v>-3016.488933984219</v>
+        <v>-3075.767210920556</v>
       </c>
       <c r="D89">
-        <v>964.0930660157809</v>
+        <v>954.3007890794444</v>
       </c>
       <c r="E89">
-        <v>4289.182</v>
+        <v>4338.668</v>
       </c>
       <c r="F89">
-        <v>4305.282</v>
+        <v>4354.768</v>
       </c>
       <c r="G89">
         <v>324.7</v>
@@ -8716,37 +8716,37 @@
         <v>330.89</v>
       </c>
       <c r="M89">
-        <v>1015.1854956</v>
+        <v>1026.8542944</v>
       </c>
       <c r="N89">
-        <v>-684.2954956000001</v>
+        <v>-695.9642944</v>
       </c>
       <c r="O89">
-        <v>-171.0738739</v>
+        <v>-173.9910736</v>
       </c>
       <c r="P89">
-        <v>-513.2216217</v>
+        <v>-521.9732208</v>
       </c>
       <c r="Q89">
-        <v>-506.0116217</v>
+        <v>-514.7632208</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2533734924527296</v>
+        <v>0.2706712834904571</v>
       </c>
       <c r="T89">
-        <v>4.045993724242028</v>
+        <v>4.383159867928865</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.08148510824724593</v>
+        <v>0.08055914110807268</v>
       </c>
       <c r="W89">
-        <v>0.2165858114752994</v>
+        <v>0.2168041545267165</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3259404329889837</v>
+        <v>0.3222365644322908</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8762,22 +8762,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2232682100023654</v>
+        <v>0.2251682100023653</v>
       </c>
       <c r="C90">
-        <v>-3075.767210920556</v>
+        <v>-3134.848567986824</v>
       </c>
       <c r="D90">
-        <v>954.3007890794444</v>
+        <v>944.7054320131765</v>
       </c>
       <c r="E90">
-        <v>4338.668</v>
+        <v>4388.154</v>
       </c>
       <c r="F90">
-        <v>4354.768</v>
+        <v>4404.254000000001</v>
       </c>
       <c r="G90">
         <v>324.7</v>
@@ -8798,37 +8798,37 @@
         <v>330.89</v>
       </c>
       <c r="M90">
-        <v>1026.8542944</v>
+        <v>1038.5230932</v>
       </c>
       <c r="N90">
-        <v>-695.9642944</v>
+        <v>-707.6330932000001</v>
       </c>
       <c r="O90">
-        <v>-173.9910736</v>
+        <v>-176.9082733</v>
       </c>
       <c r="P90">
-        <v>-521.9732208</v>
+        <v>-530.7248199000001</v>
       </c>
       <c r="Q90">
-        <v>-514.7632208</v>
+        <v>-523.5148199</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2706712834904571</v>
+        <v>0.2911141274441351</v>
       </c>
       <c r="T90">
-        <v>4.383159867928865</v>
+        <v>4.781628946831489</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.08055914110807268</v>
+        <v>0.07965398221921792</v>
       </c>
       <c r="W90">
-        <v>0.2168041545267165</v>
+        <v>0.2170175909927084</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3222365644322908</v>
+        <v>0.3186159288768717</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8844,22 +8844,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2251682100023653</v>
+        <v>0.2270682100023654</v>
       </c>
       <c r="C91">
-        <v>-3134.848567986824</v>
+        <v>-3193.73888605455</v>
       </c>
       <c r="D91">
-        <v>944.7054320131765</v>
+        <v>935.3011139454508</v>
       </c>
       <c r="E91">
-        <v>4388.154</v>
+        <v>4437.64</v>
       </c>
       <c r="F91">
-        <v>4404.254000000001</v>
+        <v>4453.740000000001</v>
       </c>
       <c r="G91">
         <v>324.7</v>
@@ -8880,37 +8880,37 @@
         <v>330.89</v>
       </c>
       <c r="M91">
-        <v>1038.5230932</v>
+        <v>1050.191892</v>
       </c>
       <c r="N91">
-        <v>-707.6330932000001</v>
+        <v>-719.3018920000002</v>
       </c>
       <c r="O91">
-        <v>-176.9082733</v>
+        <v>-179.825473</v>
       </c>
       <c r="P91">
-        <v>-530.7248199000001</v>
+        <v>-539.4764190000001</v>
       </c>
       <c r="Q91">
-        <v>-523.5148199</v>
+        <v>-532.266419</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2911141274441351</v>
+        <v>0.3156455401885486</v>
       </c>
       <c r="T91">
-        <v>4.781628946831489</v>
+        <v>5.259791841514637</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.07965398221921792</v>
+        <v>0.07876893797233772</v>
       </c>
       <c r="W91">
-        <v>0.2170175909927084</v>
+        <v>0.2172262844261228</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3186159288768717</v>
+        <v>0.3150757518893509</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8926,22 +8926,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2270682100023654</v>
+        <v>0.2289682100023653</v>
       </c>
       <c r="C92">
-        <v>-3193.73888605455</v>
+        <v>-3252.443814132683</v>
       </c>
       <c r="D92">
-        <v>935.3011139454508</v>
+        <v>926.0821858673179</v>
       </c>
       <c r="E92">
-        <v>4437.64</v>
+        <v>4487.126</v>
       </c>
       <c r="F92">
-        <v>4453.740000000001</v>
+        <v>4503.226000000001</v>
       </c>
       <c r="G92">
         <v>324.7</v>
@@ -8962,37 +8962,37 @@
         <v>330.89</v>
       </c>
       <c r="M92">
-        <v>1050.191892</v>
+        <v>1061.8606908</v>
       </c>
       <c r="N92">
-        <v>-719.3018920000002</v>
+        <v>-730.9706908000001</v>
       </c>
       <c r="O92">
-        <v>-179.825473</v>
+        <v>-182.7426727</v>
       </c>
       <c r="P92">
-        <v>-539.4764190000001</v>
+        <v>-548.2280181000001</v>
       </c>
       <c r="Q92">
-        <v>-532.266419</v>
+        <v>-541.0180181000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3156455401885486</v>
+        <v>0.3456283779872762</v>
       </c>
       <c r="T92">
-        <v>5.259791841514637</v>
+        <v>5.844213157238488</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.07876893797233772</v>
+        <v>0.07790334524736699</v>
       </c>
       <c r="W92">
-        <v>0.2172262844261228</v>
+        <v>0.2174303911906709</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3150757518893509</v>
+        <v>0.311613380989468</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9008,22 +9008,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2289682100023653</v>
+        <v>0.2308682100023654</v>
       </c>
       <c r="C93">
-        <v>-3252.443814132683</v>
+        <v>-3310.968780682995</v>
       </c>
       <c r="D93">
-        <v>926.0821858673179</v>
+        <v>917.0432193170058</v>
       </c>
       <c r="E93">
-        <v>4487.126</v>
+        <v>4536.612</v>
       </c>
       <c r="F93">
-        <v>4503.226000000001</v>
+        <v>4552.712</v>
       </c>
       <c r="G93">
         <v>324.7</v>
@@ -9044,37 +9044,37 @@
         <v>330.89</v>
       </c>
       <c r="M93">
-        <v>1061.8606908</v>
+        <v>1073.5294896</v>
       </c>
       <c r="N93">
-        <v>-730.9706908000001</v>
+        <v>-742.6394896000002</v>
       </c>
       <c r="O93">
-        <v>-182.7426727</v>
+        <v>-185.6598724</v>
       </c>
       <c r="P93">
-        <v>-548.2280181000001</v>
+        <v>-556.9796172000001</v>
       </c>
       <c r="Q93">
-        <v>-541.0180181000001</v>
+        <v>-549.7696172000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3456283779872762</v>
+        <v>0.3831069252356858</v>
       </c>
       <c r="T93">
-        <v>5.844213157238488</v>
+        <v>6.574739801893299</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.07790334524736699</v>
+        <v>0.07705656975554777</v>
       </c>
       <c r="W93">
-        <v>0.2174303911906709</v>
+        <v>0.2176300608516419</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.311613380989468</v>
+        <v>0.3082262790221911</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9090,22 +9090,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2308682100023654</v>
+        <v>0.2327682100023654</v>
       </c>
       <c r="C94">
-        <v>-3310.968780682995</v>
+        <v>-3369.319004279228</v>
       </c>
       <c r="D94">
-        <v>917.0432193170058</v>
+        <v>908.1789957207725</v>
       </c>
       <c r="E94">
-        <v>4536.612</v>
+        <v>4586.098</v>
       </c>
       <c r="F94">
-        <v>4552.712</v>
+        <v>4602.198</v>
       </c>
       <c r="G94">
         <v>324.7</v>
@@ -9126,37 +9126,37 @@
         <v>330.89</v>
       </c>
       <c r="M94">
-        <v>1073.5294896</v>
+        <v>1085.1982884</v>
       </c>
       <c r="N94">
-        <v>-742.6394896000002</v>
+        <v>-754.3082884</v>
       </c>
       <c r="O94">
-        <v>-185.6598724</v>
+        <v>-188.5770721</v>
       </c>
       <c r="P94">
-        <v>-556.9796172000001</v>
+        <v>-565.7312163</v>
       </c>
       <c r="Q94">
-        <v>-549.7696172000001</v>
+        <v>-558.5212163</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3831069252356858</v>
+        <v>0.4312936288407839</v>
       </c>
       <c r="T94">
-        <v>6.574739801893299</v>
+        <v>7.513988345020915</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.07705656975554777</v>
+        <v>0.07622800448935908</v>
       </c>
       <c r="W94">
-        <v>0.2176300608516419</v>
+        <v>0.2178254365414092</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9164,7 +9164,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3082262790221911</v>
+        <v>0.3049120179574364</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9172,22 +9172,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2327682100023654</v>
+        <v>0.2346682100023654</v>
       </c>
       <c r="C95">
-        <v>-3369.319004279228</v>
+        <v>-3427.499503653963</v>
       </c>
       <c r="D95">
-        <v>908.1789957207725</v>
+        <v>899.4844963460374</v>
       </c>
       <c r="E95">
-        <v>4586.098</v>
+        <v>4635.584</v>
       </c>
       <c r="F95">
-        <v>4602.198</v>
+        <v>4651.684</v>
       </c>
       <c r="G95">
         <v>324.7</v>
@@ -9208,37 +9208,37 @@
         <v>330.89</v>
       </c>
       <c r="M95">
-        <v>1085.1982884</v>
+        <v>1096.8670872</v>
       </c>
       <c r="N95">
-        <v>-754.3082884</v>
+        <v>-765.9770871999999</v>
       </c>
       <c r="O95">
-        <v>-188.5770721</v>
+        <v>-191.4942718</v>
       </c>
       <c r="P95">
-        <v>-565.7312163</v>
+        <v>-574.4828153999999</v>
       </c>
       <c r="Q95">
-        <v>-558.5212163</v>
+        <v>-567.2728153999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4312936288407839</v>
+        <v>0.4955425669809146</v>
       </c>
       <c r="T95">
-        <v>7.513988345020915</v>
+        <v>8.766319735857737</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.07622800448935908</v>
+        <v>0.07541706827138719</v>
       </c>
       <c r="W95">
-        <v>0.2178254365414092</v>
+        <v>0.2180166553016069</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9246,7 +9246,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3049120179574364</v>
+        <v>0.3016682730855488</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9254,22 +9254,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2346682100023654</v>
+        <v>0.2365682100023653</v>
       </c>
       <c r="C96">
-        <v>-3427.499503653963</v>
+        <v>-3485.515107173857</v>
       </c>
       <c r="D96">
-        <v>899.4844963460374</v>
+        <v>890.9548928261436</v>
       </c>
       <c r="E96">
-        <v>4635.584</v>
+        <v>4685.070000000001</v>
       </c>
       <c r="F96">
-        <v>4651.684</v>
+        <v>4701.170000000001</v>
       </c>
       <c r="G96">
         <v>324.7</v>
@@ -9290,37 +9290,37 @@
         <v>330.89</v>
       </c>
       <c r="M96">
-        <v>1096.8670872</v>
+        <v>1108.535886</v>
       </c>
       <c r="N96">
-        <v>-765.9770871999999</v>
+        <v>-777.6458860000002</v>
       </c>
       <c r="O96">
-        <v>-191.4942718</v>
+        <v>-194.4114715000001</v>
       </c>
       <c r="P96">
-        <v>-574.4828153999999</v>
+        <v>-583.2344145000002</v>
       </c>
       <c r="Q96">
-        <v>-567.2728153999999</v>
+        <v>-576.0244145000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4955425669809146</v>
+        <v>0.5854910803770977</v>
       </c>
       <c r="T96">
-        <v>8.766319735857737</v>
+        <v>10.51958368302929</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.07541706827138719</v>
+        <v>0.07462320439484625</v>
       </c>
       <c r="W96">
-        <v>0.2180166553016069</v>
+        <v>0.2182038484036952</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3016682730855488</v>
+        <v>0.2984928175793851</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9336,22 +9336,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2365682100023653</v>
+        <v>0.2384682100023654</v>
       </c>
       <c r="C97">
-        <v>-3485.515107173857</v>
+        <v>-3543.370461780839</v>
       </c>
       <c r="D97">
-        <v>890.9548928261436</v>
+        <v>882.5855382191622</v>
       </c>
       <c r="E97">
-        <v>4685.070000000001</v>
+        <v>4734.556</v>
       </c>
       <c r="F97">
-        <v>4701.170000000001</v>
+        <v>4750.656000000001</v>
       </c>
       <c r="G97">
         <v>324.7</v>
@@ -9372,37 +9372,37 @@
         <v>330.89</v>
       </c>
       <c r="M97">
-        <v>1108.535886</v>
+        <v>1120.2046848</v>
       </c>
       <c r="N97">
-        <v>-777.6458860000002</v>
+        <v>-789.3146848000001</v>
       </c>
       <c r="O97">
-        <v>-194.4114715000001</v>
+        <v>-197.3286712</v>
       </c>
       <c r="P97">
-        <v>-583.2344145000002</v>
+        <v>-591.9860136000001</v>
       </c>
       <c r="Q97">
-        <v>-576.0244145000001</v>
+        <v>-584.7760136000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.5854910803770977</v>
+        <v>0.7204138504713726</v>
       </c>
       <c r="T97">
-        <v>10.51958368302929</v>
+        <v>13.14947960378662</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.07462320439484625</v>
+        <v>0.07384587934906661</v>
       </c>
       <c r="W97">
-        <v>0.2182038484036952</v>
+        <v>0.2183871416494901</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9410,7 +9410,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2984928175793851</v>
+        <v>0.2953835173962664</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9418,22 +9418,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2384682100023653</v>
+        <v>0.2403682100023654</v>
       </c>
       <c r="C98">
-        <v>-3543.370461780838</v>
+        <v>-3601.070041434042</v>
       </c>
       <c r="D98">
-        <v>882.5855382191622</v>
+        <v>874.3719585659582</v>
       </c>
       <c r="E98">
-        <v>4734.556</v>
+        <v>4784.041999999999</v>
       </c>
       <c r="F98">
-        <v>4750.656</v>
+        <v>4800.142</v>
       </c>
       <c r="G98">
         <v>324.7</v>
@@ -9454,37 +9454,37 @@
         <v>330.89</v>
       </c>
       <c r="M98">
-        <v>1120.2046848</v>
+        <v>1131.8734836</v>
       </c>
       <c r="N98">
-        <v>-789.3146847999999</v>
+        <v>-800.9834836</v>
       </c>
       <c r="O98">
-        <v>-197.3286712</v>
+        <v>-200.2458709</v>
       </c>
       <c r="P98">
-        <v>-591.9860136</v>
+        <v>-600.7376127</v>
       </c>
       <c r="Q98">
-        <v>-584.7760135999999</v>
+        <v>-593.5276127</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7204138504713706</v>
+        <v>0.9452851339618278</v>
       </c>
       <c r="T98">
-        <v>13.14947960378658</v>
+        <v>17.53263947171545</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.07384587934906663</v>
+        <v>0.07308458162381851</v>
       </c>
       <c r="W98">
-        <v>0.2183871416494901</v>
+        <v>0.2185666556531036</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9492,7 +9492,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2953835173962666</v>
+        <v>0.2923383264952741</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9500,22 +9500,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2403682100023654</v>
+        <v>0.2422682100023653</v>
       </c>
       <c r="C99">
-        <v>-3601.070041434042</v>
+        <v>-3658.618155084719</v>
       </c>
       <c r="D99">
-        <v>874.3719585659582</v>
+        <v>866.3098449152823</v>
       </c>
       <c r="E99">
-        <v>4784.041999999999</v>
+        <v>4833.528</v>
       </c>
       <c r="F99">
-        <v>4800.142</v>
+        <v>4849.628000000001</v>
       </c>
       <c r="G99">
         <v>324.7</v>
@@ -9536,37 +9536,37 @@
         <v>330.89</v>
       </c>
       <c r="M99">
-        <v>1131.8734836</v>
+        <v>1143.5422824</v>
       </c>
       <c r="N99">
-        <v>-800.9834836</v>
+        <v>-812.6522824000001</v>
       </c>
       <c r="O99">
-        <v>-200.2458709</v>
+        <v>-203.1630706</v>
       </c>
       <c r="P99">
-        <v>-600.7376127</v>
+        <v>-609.4892118</v>
       </c>
       <c r="Q99">
-        <v>-593.5276127</v>
+        <v>-602.2792118</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9452851339618278</v>
+        <v>1.395027700942741</v>
       </c>
       <c r="T99">
-        <v>17.53263947171545</v>
+        <v>26.29895920757316</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.07308458162381851</v>
+        <v>0.07233882058684077</v>
       </c>
       <c r="W99">
-        <v>0.2185666556531036</v>
+        <v>0.218742506105623</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2923383264952741</v>
+        <v>0.2893552823473631</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9582,22 +9582,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2422682100023653</v>
+        <v>0.2441682100023653</v>
       </c>
       <c r="C100">
-        <v>-3658.618155084719</v>
+        <v>-3716.018954213975</v>
       </c>
       <c r="D100">
-        <v>866.3098449152823</v>
+        <v>858.3950457860252</v>
       </c>
       <c r="E100">
-        <v>4833.528</v>
+        <v>4883.014</v>
       </c>
       <c r="F100">
-        <v>4849.628000000001</v>
+        <v>4899.114</v>
       </c>
       <c r="G100">
         <v>324.7</v>
@@ -9618,37 +9618,37 @@
         <v>330.89</v>
       </c>
       <c r="M100">
-        <v>1143.5422824</v>
+        <v>1155.2110812</v>
       </c>
       <c r="N100">
-        <v>-812.6522824000001</v>
+        <v>-824.3210812</v>
       </c>
       <c r="O100">
-        <v>-203.1630706</v>
+        <v>-206.0802703</v>
       </c>
       <c r="P100">
-        <v>-609.4892118</v>
+        <v>-618.2408109</v>
       </c>
       <c r="Q100">
-        <v>-602.2792118</v>
+        <v>-611.0308109</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.395027700942741</v>
+        <v>2.744255401885483</v>
       </c>
       <c r="T100">
-        <v>26.29895920757316</v>
+        <v>52.59791841514632</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.07233882058684077</v>
+        <v>0.07160812542939794</v>
       </c>
       <c r="W100">
-        <v>0.218742506105623</v>
+        <v>0.218914804023748</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9656,91 +9656,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2893552823473631</v>
+        <v>0.2864325017175918</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2441682100023653</v>
-      </c>
-      <c r="C101">
-        <v>-3716.018954213975</v>
-      </c>
-      <c r="D101">
-        <v>858.3950457860252</v>
-      </c>
-      <c r="E101">
-        <v>4883.014</v>
-      </c>
-      <c r="F101">
-        <v>4899.114</v>
-      </c>
-      <c r="G101">
-        <v>324.7</v>
-      </c>
-      <c r="H101">
-        <v>4932.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>338.1</v>
-      </c>
-      <c r="K101">
-        <v>7.21</v>
-      </c>
-      <c r="L101">
-        <v>330.89</v>
-      </c>
-      <c r="M101">
-        <v>1155.2110812</v>
-      </c>
-      <c r="N101">
-        <v>-824.3210812</v>
-      </c>
-      <c r="O101">
-        <v>-206.0802703</v>
-      </c>
-      <c r="P101">
-        <v>-618.2408109</v>
-      </c>
-      <c r="Q101">
-        <v>-611.0308109</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.744255401885483</v>
-      </c>
-      <c r="T101">
-        <v>52.59791841514632</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.07160812542939794</v>
-      </c>
-      <c r="W101">
-        <v>0.218914804023748</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2864325017175918</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
